--- a/source/pipeline.xlsx
+++ b/source/pipeline.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\enterprise\omega\Папки отделов\Департамент закупівель та логістики\Відділ реінжинірингу процесів закупівель\Master data\З'єднувач\обработка\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2297BCA9-EC4E-4CD8-B12B-E7E5969BC329}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9366B9C8-665C-474E-A6FF-A6E4F096964A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2688" uniqueCount="999">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3842" uniqueCount="1409">
   <si>
     <t>Номер карточки</t>
   </si>
@@ -6535,6 +6535,1630 @@
   </si>
   <si>
     <t>Товарное наименование</t>
+  </si>
+  <si>
+    <t>_23471364585</t>
+  </si>
+  <si>
+    <t>_Н.036.81.0485 1SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 1SN ID 8 мм, L=485 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 1-слойно-армированный комбинированно-армированный с лайнером резина NBR 1SN ID 8 мм, 215 бар, L=485 мм, гайка M16×1.5 S19 / гайка M16×1.5 S19</t>
+  </si>
+  <si>
+    <t>Продуктовая семья: Соединители
+Продуктовая категория: Трубопроводы жесткие и гибкие
+Конструктивная основа: непрерывный проводящий канал
+Определённый термин: Рукав высокого давления в сборе
+Конструктивная форма и гибкость: изгибается свободно и не сохраняет форму без фиксации
+Материал основы: резина
+Рабочая среда: гидравлическая жидкость
+Размерная модель: параметрический (ID / OD / толщина стенки)
+Размер: ID 8 мм
+Сокращение в пользовательском наименовании: модифицированный
+Внутренний слой / лайнер: да
+Материал лайнера: резина NBR
+Единица продажи: шт (штучное изделие)
+Монтажная геометрия изделия: гладкий
+Профиль канала: гладкий
+Исполнение изделия: прямой
+Конструкция стенки: армированная
+Количество слоёв / слоёв армирования: 1
+Армирование: комбинированное
+Рабочее давление: 215 бар
+Температура max: 100 °C
+Стандарт / серия: 1SN
+Конструктивная расшифровка стандарта: однослойная металлическая оплётка
+Наличие портов: с двух сторон
+Порт A: гайка M16×1.5 S19
+Порт B: гайка M16×1.5 S19</t>
+  </si>
+  <si>
+    <t>Поисковые альтернативы:
+• РВД
+• рукав ВД
+• гидравлический рукав
+• рукав 1SN
+• МБС
+• маслобензостойкий
+• рукав высокого давления ID 8 мм</t>
+  </si>
+  <si>
+    <t>_23471364586</t>
+  </si>
+  <si>
+    <t>_Н.036.81.0590 1SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 1SN ID 8 мм, L=590 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 1-слойно-армированный комбинированно-армированный с лайнером резина NBR 1SN ID 8 мм, 215 бар, L=590 мм, гайка M16×1.5 S19 / гайка M16×1.5 S19</t>
+  </si>
+  <si>
+    <t>_23471364587</t>
+  </si>
+  <si>
+    <t>_Н.036.81.0610 1SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 1SN ID 8 мм, L=610 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 1-слойно-армированный комбинированно-армированный с лайнером резина NBR 1SN ID 8 мм, 215 бар, L=610 мм, гайка M16×1.5 S19 / гайка M16×1.5 S19</t>
+  </si>
+  <si>
+    <t>_23471364588</t>
+  </si>
+  <si>
+    <t>_Н.036.81.0750 1SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 1SN ID 8 мм, L=750 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 1-слойно-армированный комбинированно-армированный с лайнером резина NBR 1SN ID 8 мм, 215 бар, L=750 мм, гайка M16×1.5 S19 / гайка M16×1.5 S19</t>
+  </si>
+  <si>
+    <t>_23471364589</t>
+  </si>
+  <si>
+    <t>_Н.036.81.0810 1SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 1SN ID 8 мм, L=810 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 1-слойно-армированный комбинированно-армированный с лайнером резина NBR 1SN ID 8 мм, 215 бар, L=810 мм, гайка M16×1.5 S19 / гайка M16×1.5 S19</t>
+  </si>
+  <si>
+    <t>_23471364590</t>
+  </si>
+  <si>
+    <t>_Н.036.81.1010 1SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 1SN ID 8 мм, L=1010 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 1-слойно-армированный комбинированно-армированный с лайнером резина NBR 1SN ID 8 мм, 215 бар, L=1010 мм, гайка M16×1.5 S19 / гайка M16×1.5 S19</t>
+  </si>
+  <si>
+    <t>_23471364591</t>
+  </si>
+  <si>
+    <t>_Н.036.81.1210 1SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 1SN ID 8 мм, L=1210 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 1-слойно-армированный комбинированно-армированный с лайнером резина NBR 1SN ID 8 мм, 215 бар, L=1210 мм, гайка M16×1.5 S19 / гайка M16×1.5 S19</t>
+  </si>
+  <si>
+    <t>_23471364592</t>
+  </si>
+  <si>
+    <t>_Н.036.81.1410 1SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 1SN ID 8 мм, L=1410 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 1-слойно-армированный комбинированно-армированный с лайнером резина NBR 1SN ID 8 мм, 215 бар, L=1410 мм, гайка M16×1.5 S19 / гайка M16×1.5 S19</t>
+  </si>
+  <si>
+    <t>_23471364593</t>
+  </si>
+  <si>
+    <t>_Н.036.81.1610 1SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 1SN ID 8 мм, L=1610 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 1-слойно-армированный комбинированно-армированный с лайнером резина NBR 1SN ID 8 мм, 215 бар, L=1610 мм, гайка M16×1.5 S19 / гайка M16×1.5 S19</t>
+  </si>
+  <si>
+    <t>_23471364594</t>
+  </si>
+  <si>
+    <t>_Н.036.81.2010 1SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 1SN ID 8 мм, L=2010 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 1-слойно-армированный комбинированно-армированный с лайнером резина NBR 1SN ID 8 мм, 215 бар, L=2010 мм, гайка M16×1.5 S19 / гайка M16×1.5 S19</t>
+  </si>
+  <si>
+    <t>_23471364595</t>
+  </si>
+  <si>
+    <t>_Н.036.82.0610 1SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 1SN ID 10 мм, L=610 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 1-слойно-армированный комбинированно-армированный с лайнером резина NBR 1SN ID 10 мм, 180 бар, L=610 мм, гайка M18×1.5 S22 / гайка M18×1.5 S22</t>
+  </si>
+  <si>
+    <t>Продуктовая семья: Соединители
+Продуктовая категория: Трубопроводы жесткие и гибкие
+Конструктивная основа: непрерывный проводящий канал
+Определённый термин: Рукав высокого давления в сборе
+Конструктивная форма и гибкость: изгибается свободно и не сохраняет форму без фиксации
+Материал основы: резина
+Рабочая среда: гидравлическая жидкость
+Размерная модель: параметрический (ID / OD / толщина стенки)
+Размер: ID 10 мм
+Сокращение в пользовательском наименовании: модифицированный
+Внутренний слой / лайнер: да
+Материал лайнера: резина NBR
+Единица продажи: шт (штучное изделие)
+Монтажная геометрия изделия: гладкий
+Профиль канала: гладкий
+Исполнение изделия: прямой
+Конструкция стенки: армированная
+Количество слоёв / слоёв армирования: 1
+Армирование: комбинированное
+Рабочее давление: 180 бар
+Температура max: 100 °C
+Стандарт / серия: 1SN
+Конструктивная расшифровка стандарта: однослойная металлическая оплётка
+Наличие портов: с двух сторон
+Порт A: гайка M18×1.5 S22
+Порт B: гайка M18×1.5 S22</t>
+  </si>
+  <si>
+    <t>Поисковые альтернативы:
+• РВД
+• рукав ВД
+• гидравлический рукав
+• рукав 1SN
+• МБС
+• маслобензостойкий
+• рукав высокого давления ID 10 мм</t>
+  </si>
+  <si>
+    <t>_23471364596</t>
+  </si>
+  <si>
+    <t>_Н.036.82.1410 1SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 1SN ID 10 мм, L=1410 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 1-слойно-армированный комбинированно-армированный с лайнером резина NBR 1SN ID 10 мм, 180 бар, L=1410 мм, гайка M18×1.5 S22 / гайка M18×1.5 S22</t>
+  </si>
+  <si>
+    <t>_23471364597</t>
+  </si>
+  <si>
+    <t>_Н.036.83.0510 1SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 1SN ID 12 мм, L=510 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 1-слойно-армированный комбинированно-армированный с лайнером резина NBR 1SN ID 12 мм, 160 бар, L=510 мм, гайка M20×1.5 S24 / гайка M20×1.5 S24</t>
+  </si>
+  <si>
+    <t>Продуктовая семья: Соединители
+Продуктовая категория: Трубопроводы жесткие и гибкие
+Конструктивная основа: непрерывный проводящий канал
+Определённый термин: Рукав высокого давления в сборе
+Конструктивная форма и гибкость: изгибается свободно и не сохраняет форму без фиксации
+Материал основы: резина
+Рабочая среда: гидравлическая жидкость
+Размерная модель: параметрический (ID / OD / толщина стенки)
+Размер: ID 12 мм
+Сокращение в пользовательском наименовании: модифицированный
+Внутренний слой / лайнер: да
+Материал лайнера: резина NBR
+Единица продажи: шт (штучное изделие)
+Монтажная геометрия изделия: гладкий
+Профиль канала: гладкий
+Исполнение изделия: прямой
+Конструкция стенки: армированная
+Количество слоёв / слоёв армирования: 1
+Армирование: комбинированное
+Рабочее давление: 160 бар
+Температура max: 100 °C
+Стандарт / серия: 1SN
+Конструктивная расшифровка стандарта: однослойная металлическая оплётка
+Наличие портов: с двух сторон
+Порт A: гайка M20×1.5 S24
+Порт B: гайка M20×1.5 S24</t>
+  </si>
+  <si>
+    <t>Поисковые альтернативы:
+• РВД
+• рукав ВД
+• гидравлический рукав
+• рукав 1SN
+• МБС
+• маслобензостойкий
+• рукав высокого давления ID 12 мм</t>
+  </si>
+  <si>
+    <t>_23471364598</t>
+  </si>
+  <si>
+    <t>_Н.036.83.0610 1SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 1SN ID 12 мм, L=610 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 1-слойно-армированный комбинированно-армированный с лайнером резина NBR 1SN ID 12 мм, 160 бар, L=610 мм, гайка M20×1.5 S24 / гайка M20×1.5 S24</t>
+  </si>
+  <si>
+    <t>_23471364599</t>
+  </si>
+  <si>
+    <t>_Н.036.83.0810 1SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 1SN ID 12 мм, L=810 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 1-слойно-армированный комбинированно-армированный с лайнером резина NBR 1SN ID 12 мм, 160 бар, L=810 мм, гайка M20×1.5 S24 / гайка M20×1.5 S24</t>
+  </si>
+  <si>
+    <t>_23471364600</t>
+  </si>
+  <si>
+    <t>_Н.036.83.1010 1SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 1SN ID 12 мм, L=1010 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 1-слойно-армированный комбинированно-армированный с лайнером резина NBR 1SN ID 12 мм, 160 бар, L=1010 мм, гайка M20×1.5 S24 / гайка M20×1.5 S24</t>
+  </si>
+  <si>
+    <t>_23471364601</t>
+  </si>
+  <si>
+    <t>_Н.036.83.1210 1SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 1SN ID 12 мм, L=1210 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 1-слойно-армированный комбинированно-армированный с лайнером резина NBR 1SN ID 12 мм, 160 бар, L=1210 мм, гайка M20×1.5 S24 / гайка M20×1.5 S24</t>
+  </si>
+  <si>
+    <t>_23471364602</t>
+  </si>
+  <si>
+    <t>_Н.036.83.1410 1SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 1SN ID 12 мм, L=1410 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 1-слойно-армированный комбинированно-армированный с лайнером резина NBR 1SN ID 12 мм, 160 бар, L=1410 мм, гайка M20×1.5 S24 / гайка M20×1.5 S24</t>
+  </si>
+  <si>
+    <t>_23471364603</t>
+  </si>
+  <si>
+    <t>_Н.036.83.1510 1SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 1SN ID 12 мм, L=1510 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 1-слойно-армированный комбинированно-армированный с лайнером резина NBR 1SN ID 12 мм, 160 бар, L=1510 мм, гайка M20×1.5 S24 / гайка M20×1.5 S24</t>
+  </si>
+  <si>
+    <t>_23471364604</t>
+  </si>
+  <si>
+    <t>_Н.036.83.1610 1SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 1SN ID 12 мм, L=1610 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 1-слойно-армированный комбинированно-армированный с лайнером резина NBR 1SN ID 12 мм, 160 бар, L=1610 мм, гайка M20×1.5 S24 / гайка M20×1.5 S24</t>
+  </si>
+  <si>
+    <t>_23471364605</t>
+  </si>
+  <si>
+    <t>_Н.036.83.1810 1SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 1SN ID 12 мм, L=1810 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 1-слойно-армированный комбинированно-армированный с лайнером резина NBR 1SN ID 12 мм, 160 бар, L=1810 мм, гайка M20×1.5 S24 / гайка M20×1.5 S24</t>
+  </si>
+  <si>
+    <t>_23471364606</t>
+  </si>
+  <si>
+    <t>_Н.036.83.2010 1SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 1SN ID 12 мм, L=2010 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 1-слойно-армированный комбинированно-армированный с лайнером резина NBR 1SN ID 12 мм, 160 бар, L=2010 мм, гайка M20×1.5 S24 / гайка M20×1.5 S24</t>
+  </si>
+  <si>
+    <t>_23471364607</t>
+  </si>
+  <si>
+    <t>_Н.036.84.0610 1SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 1-слойно-армированный комбинированно-армированный с лайнером резина NBR 1SN ID 12 мм, 160 бар, L=610 мм, гайка M22×1.5 S27 / гайка M22×1.5 S27</t>
+  </si>
+  <si>
+    <t>Продуктовая семья: Соединители
+Продуктовая категория: Трубопроводы жесткие и гибкие
+Конструктивная основа: непрерывный проводящий канал
+Определённый термин: Рукав высокого давления в сборе
+Конструктивная форма и гибкость: изгибается свободно и не сохраняет форму без фиксации
+Материал основы: резина
+Рабочая среда: гидравлическая жидкость
+Размерная модель: параметрический (ID / OD / толщина стенки)
+Размер: ID 12 мм
+Сокращение в пользовательском наименовании: модифицированный
+Внутренний слой / лайнер: да
+Материал лайнера: резина NBR
+Единица продажи: шт (штучное изделие)
+Монтажная геометрия изделия: гладкий
+Профиль канала: гладкий
+Исполнение изделия: прямой
+Конструкция стенки: армированная
+Количество слоёв / слоёв армирования: 1
+Армирование: комбинированное
+Рабочее давление: 160 бар
+Температура max: 100 °C
+Стандарт / серия: 1SN
+Конструктивная расшифровка стандарта: однослойная металлическая оплётка
+Наличие портов: с двух сторон
+Порт A: гайка M22×1.5 S27
+Порт B: гайка M22×1.5 S27</t>
+  </si>
+  <si>
+    <t>_23471364608</t>
+  </si>
+  <si>
+    <t>_Н.036.84.0810 1SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 1-слойно-армированный комбинированно-армированный с лайнером резина NBR 1SN ID 12 мм, 160 бар, L=810 мм, гайка M22×1.5 S27 / гайка M22×1.5 S27</t>
+  </si>
+  <si>
+    <t>_23471364609</t>
+  </si>
+  <si>
+    <t>_Н.036.84.1010 1SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 1-слойно-армированный комбинированно-армированный с лайнером резина NBR 1SN ID 12 мм, 160 бар, L=1010 мм, гайка M22×1.5 S27 / гайка M22×1.5 S27</t>
+  </si>
+  <si>
+    <t>_23471364610</t>
+  </si>
+  <si>
+    <t>_Н.036.84.1210 1SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 1-слойно-армированный комбинированно-армированный с лайнером резина NBR 1SN ID 12 мм, 160 бар, L=1210 мм, гайка M22×1.5 S27 / гайка M22×1.5 S27</t>
+  </si>
+  <si>
+    <t>_23471364611</t>
+  </si>
+  <si>
+    <t>_Н.036.84.1610 1SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 1-слойно-армированный комбинированно-армированный с лайнером резина NBR 1SN ID 12 мм, 160 бар, L=1610 мм, гайка M22×1.5 S27 / гайка M22×1.5 S27</t>
+  </si>
+  <si>
+    <t>_23471364612</t>
+  </si>
+  <si>
+    <t>_Н.036.85.0610 1SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 1SN ID 16 мм, L=610 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 1-слойно-армированный комбинированно-армированный с лайнером резина NBR 1SN ID 16 мм, 130 бар, L=610 мм, гайка M S32 / гайка M S32</t>
+  </si>
+  <si>
+    <t>Продуктовая семья: Соединители
+Продуктовая категория: Трубопроводы жесткие и гибкие
+Конструктивная основа: непрерывный проводящий канал
+Определённый термин: Рукав высокого давления в сборе
+Конструктивная форма и гибкость: изгибается свободно и не сохраняет форму без фиксации
+Материал основы: резина
+Рабочая среда: гидравлическая жидкость
+Размерная модель: параметрический (ID / OD / толщина стенки)
+Размер: ID 16 мм
+Сокращение в пользовательском наименовании: модифицированный
+Внутренний слой / лайнер: да
+Материал лайнера: резина NBR
+Единица продажи: шт (штучное изделие)
+Монтажная геометрия изделия: гладкий
+Профиль канала: гладкий
+Исполнение изделия: прямой
+Конструкция стенки: армированная
+Количество слоёв / слоёв армирования: 1
+Армирование: комбинированное
+Рабочее давление: 130 бар
+Температура max: 100 °C
+Стандарт / серия: 1SN
+Конструктивная расшифровка стандарта: однослойная металлическая оплётка
+Наличие портов: с двух сторон
+Порт A: гайка M S32
+Порт B: гайка M S32</t>
+  </si>
+  <si>
+    <t>Поисковые альтернативы:
+• РВД
+• рукав ВД
+• гидравлический рукав
+• рукав 1SN
+• МБС
+• маслобензостойкий
+• рукав высокого давления ID 16 мм</t>
+  </si>
+  <si>
+    <t>_23471364613</t>
+  </si>
+  <si>
+    <t>_Н.036.85.0810 1SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 1SN ID 16 мм, L=810 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 1-слойно-армированный комбинированно-армированный с лайнером резина NBR 1SN ID 16 мм, 130 бар, L=810 мм, гайка M S32 / гайка M S32</t>
+  </si>
+  <si>
+    <t>_23471364614</t>
+  </si>
+  <si>
+    <t>_Н.036.85.1010 1SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 1SN ID 16 мм, L=1010 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 1-слойно-армированный комбинированно-армированный с лайнером резина NBR 1SN ID 16 мм, 130 бар, L=1010 мм, гайка M S32 / гайка M S32</t>
+  </si>
+  <si>
+    <t>_23471364615</t>
+  </si>
+  <si>
+    <t>_Н.036.85.1210 1SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 1SN ID 16 мм, L=1210 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 1-слойно-армированный комбинированно-армированный с лайнером резина NBR 1SN ID 16 мм, 130 бар, L=1210 мм, гайка M S32 / гайка M S32</t>
+  </si>
+  <si>
+    <t>_23471364616</t>
+  </si>
+  <si>
+    <t>_Н.036.85.1410 1SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 1SN ID 16 мм, L=1410 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 1-слойно-армированный комбинированно-армированный с лайнером резина NBR 1SN ID 16 мм, 130 бар, L=1410 мм, гайка M S32 / гайка M S32</t>
+  </si>
+  <si>
+    <t>_23471364617</t>
+  </si>
+  <si>
+    <t>_Н.036.85.1510 1SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 1SN ID 16 мм, L=1510 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 1-слойно-армированный комбинированно-армированный с лайнером резина NBR 1SN ID 16 мм, 130 бар, L=1510 мм, гайка M S32 / гайка M S32</t>
+  </si>
+  <si>
+    <t>_23471364618</t>
+  </si>
+  <si>
+    <t>_Н.036.85.1610 1SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 1SN ID 16 мм, L=1610 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 1-слойно-армированный комбинированно-армированный с лайнером резина NBR 1SN ID 16 мм, 130 бар, L=1610 мм, гайка M S32 / гайка M S32</t>
+  </si>
+  <si>
+    <t>_23471364619</t>
+  </si>
+  <si>
+    <t>_Н.036.85.2010 1SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 1SN ID 16 мм, L=2010 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 1-слойно-армированный комбинированно-армированный с лайнером резина NBR 1SN ID 16 мм, 130 бар, L=2010 мм, гайка M S32 / гайка M S32</t>
+  </si>
+  <si>
+    <t>_23471364620</t>
+  </si>
+  <si>
+    <t>_Н.036.81.0410 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 8 мм, L=410 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 8 мм, 350 бар, L=410 мм, гайка M16×1.5 S19 / гайка M16×1.5 S19</t>
+  </si>
+  <si>
+    <t>Продуктовая семья: Соединители
+Продуктовая категория: Трубопроводы жесткие и гибкие
+Конструктивная основа: непрерывный проводящий канал
+Определённый термин: Рукав высокого давления в сборе
+Конструктивная форма и гибкость: изгибается свободно и не сохраняет форму без фиксации
+Материал основы: резина
+Рабочая среда: гидравлическая жидкость
+Размерная модель: параметрический (ID / OD / толщина стенки)
+Размер: ID 8 мм
+Сокращение в пользовательском наименовании: модифицированный
+Внутренний слой / лайнер: да
+Материал лайнера: резина NBR
+Единица продажи: шт (штучное изделие)
+Монтажная геометрия изделия: гладкий
+Профиль канала: гладкий
+Исполнение изделия: прямой
+Конструкция стенки: армированная
+Количество слоёв / слоёв армирования: 2
+Армирование: комбинированное
+Рабочее давление: 350 бар
+Температура max: 100 °C
+Стандарт / серия: 2SN
+Конструктивная расшифровка стандарта: двухслойная металлическая оплётка
+Наличие портов: с двух сторон
+Порт A: гайка M16×1.5 S19
+Порт B: гайка M16×1.5 S19</t>
+  </si>
+  <si>
+    <t>Поисковые альтернативы:
+• РВД
+• рукав ВД
+• гидравлический рукав
+• рукав 2SN
+• МБС
+• маслобензостойкий
+• рукав высокого давления ID 8 мм</t>
+  </si>
+  <si>
+    <t>_23471364621</t>
+  </si>
+  <si>
+    <t>_Н.036.81.0610 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 8 мм, L=610 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 8 мм, 350 бар, L=610 мм, гайка M16×1.5 S19 / гайка M16×1.5 S19</t>
+  </si>
+  <si>
+    <t>_23471364622</t>
+  </si>
+  <si>
+    <t>_Н.036.81.0810 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 8 мм, L=810 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 8 мм, 350 бар, L=810 мм, гайка M16×1.5 S19 / гайка M16×1.5 S19</t>
+  </si>
+  <si>
+    <t>_23471364623</t>
+  </si>
+  <si>
+    <t>_Н.036.81.1010 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 8 мм, L=1010 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 8 мм, 350 бар, L=1010 мм, гайка M16×1.5 S19 / гайка M16×1.5 S19</t>
+  </si>
+  <si>
+    <t>_23471364624</t>
+  </si>
+  <si>
+    <t>_Н.036.81.1210 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 8 мм, L=1210 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 8 мм, 350 бар, L=1210 мм, гайка M16×1.5 S19 / гайка M16×1.5 S19</t>
+  </si>
+  <si>
+    <t>_23471364625</t>
+  </si>
+  <si>
+    <t>_Н.036.81.1510 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 8 мм, L=1510 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 8 мм, 350 бар, L=1510 мм, гайка M16×1.5 S19 / гайка M16×1.5 S19</t>
+  </si>
+  <si>
+    <t>_23471364626</t>
+  </si>
+  <si>
+    <t>_Н.036.81.1610 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 8 мм, L=1610 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 8 мм, 350 бар, L=1610 мм, гайка M16×1.5 S19 / гайка M16×1.5 S19</t>
+  </si>
+  <si>
+    <t>_23471364627</t>
+  </si>
+  <si>
+    <t>_Н.036.81.2010 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 8 мм, L=2010 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 8 мм, 350 бар, L=2010 мм, гайка M16×1.5 S19 / гайка M16×1.5 S19</t>
+  </si>
+  <si>
+    <t>_23471364628</t>
+  </si>
+  <si>
+    <t>_Н.036.82.0410 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 10 мм, L=410 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 10 мм, 330 бар, L=410 мм, гайка M18×1.5 S22 / гайка M18×1.5 S22</t>
+  </si>
+  <si>
+    <t>Продуктовая семья: Соединители
+Продуктовая категория: Трубопроводы жесткие и гибкие
+Конструктивная основа: непрерывный проводящий канал
+Определённый термин: Рукав высокого давления в сборе
+Конструктивная форма и гибкость: изгибается свободно и не сохраняет форму без фиксации
+Материал основы: резина
+Рабочая среда: гидравлическая жидкость
+Размерная модель: параметрический (ID / OD / толщина стенки)
+Размер: ID 10 мм
+Сокращение в пользовательском наименовании: модифицированный
+Внутренний слой / лайнер: да
+Материал лайнера: резина NBR
+Единица продажи: шт (штучное изделие)
+Монтажная геометрия изделия: гладкий
+Профиль канала: гладкий
+Исполнение изделия: прямой
+Конструкция стенки: армированная
+Количество слоёв / слоёв армирования: 2
+Армирование: комбинированное
+Рабочее давление: 330 бар
+Температура max: 100 °C
+Стандарт / серия: 2SN
+Конструктивная расшифровка стандарта: двухслойная металлическая оплётка
+Наличие портов: с двух сторон
+Порт A: гайка M18×1.5 S22
+Порт B: гайка M18×1.5 S22</t>
+  </si>
+  <si>
+    <t>Поисковые альтернативы:
+• РВД
+• рукав ВД
+• гидравлический рукав
+• рукав 2SN
+• МБС
+• маслобензостойкий
+• рукав высокого давления ID 10 мм</t>
+  </si>
+  <si>
+    <t>_23471364629</t>
+  </si>
+  <si>
+    <t>_Н.036.82.0610 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 10 мм, L=610 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 10 мм, 330 бар, L=610 мм, гайка M18×1.5 S22 / гайка M18×1.5 S22</t>
+  </si>
+  <si>
+    <t>_23471364630</t>
+  </si>
+  <si>
+    <t>_Н.036.82.810 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 10 мм, L=810 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 10 мм, 330 бар, L=810 мм, гайка M18×1.5 S22 / гайка M18×1.5 S22</t>
+  </si>
+  <si>
+    <t>_23471364631</t>
+  </si>
+  <si>
+    <t>_Н.036.82.1010 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 10 мм, L=1010 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 10 мм, 330 бар, L=1010 мм, гайка M18×1.5 S22 / гайка M18×1.5 S22</t>
+  </si>
+  <si>
+    <t>_23471364632</t>
+  </si>
+  <si>
+    <t>_Н.036.82.1210 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 10 мм, L=1210 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 10 мм, 330 бар, L=1210 мм, гайка M18×1.5 S22 / гайка M18×1.5 S22</t>
+  </si>
+  <si>
+    <t>_23471364633</t>
+  </si>
+  <si>
+    <t>_Н.036.82.1410 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 10 мм, L=1410 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 10 мм, 330 бар, L=1410 мм, гайка M18×1.5 S22 / гайка M18×1.5 S22</t>
+  </si>
+  <si>
+    <t>_23471364634</t>
+  </si>
+  <si>
+    <t>_Н.036.82.1510 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 10 мм, L=1510 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 10 мм, 330 бар, L=1510 мм, гайка M18×1.5 S22 / гайка M18×1.5 S22</t>
+  </si>
+  <si>
+    <t>_23471364635</t>
+  </si>
+  <si>
+    <t>_Н.036.82.1610 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 10 мм, L=1610 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 10 мм, 330 бар, L=1610 мм, гайка M18×1.5 S22 / гайка M18×1.5 S22</t>
+  </si>
+  <si>
+    <t>_23471364636</t>
+  </si>
+  <si>
+    <t>_Н.036.82.1810 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 10 мм, L=1810 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 10 мм, 330 бар, L=1810 мм, гайка M18×1.5 S22 / гайка M18×1.5 S22</t>
+  </si>
+  <si>
+    <t>_23471364637</t>
+  </si>
+  <si>
+    <t>_Н.036.82.2010 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 10 мм, L=2010 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 10 мм, 330 бар, L=2010 мм, гайка M18×1.5 S22 / гайка M18×1.5 S22</t>
+  </si>
+  <si>
+    <t>_23471364638</t>
+  </si>
+  <si>
+    <t>_Н.036.83.0210 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 12 мм, L=210 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 12 мм, 275 бар, L=210 мм, гайка M20×1.5 S24 / гайка M20×1.5 S24</t>
+  </si>
+  <si>
+    <t>Продуктовая семья: Соединители
+Продуктовая категория: Трубопроводы жесткие и гибкие
+Конструктивная основа: непрерывный проводящий канал
+Определённый термин: Рукав высокого давления в сборе
+Конструктивная форма и гибкость: изгибается свободно и не сохраняет форму без фиксации
+Материал основы: резина
+Рабочая среда: гидравлическая жидкость
+Размерная модель: параметрический (ID / OD / толщина стенки)
+Размер: ID 12 мм
+Сокращение в пользовательском наименовании: модифицированный
+Внутренний слой / лайнер: да
+Материал лайнера: резина NBR
+Единица продажи: шт (штучное изделие)
+Монтажная геометрия изделия: гладкий
+Профиль канала: гладкий
+Исполнение изделия: прямой
+Конструкция стенки: армированная
+Количество слоёв / слоёв армирования: 2
+Армирование: комбинированное
+Рабочее давление: 275 бар
+Температура max: 100 °C
+Стандарт / серия: 2SN
+Конструктивная расшифровка стандарта: двухслойная металлическая оплётка
+Наличие портов: с двух сторон
+Порт A: гайка M20×1.5 S24
+Порт B: гайка M20×1.5 S24</t>
+  </si>
+  <si>
+    <t>Поисковые альтернативы:
+• РВД
+• рукав ВД
+• гидравлический рукав
+• рукав 2SN
+• МБС
+• маслобензостойкий
+• рукав высокого давления ID 12 мм</t>
+  </si>
+  <si>
+    <t>_23471364639</t>
+  </si>
+  <si>
+    <t>_Н.036.83.0410 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 12 мм, L=410 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 12 мм, 275 бар, L=410 мм, гайка M20×1.5 S24 / гайка M20×1.5 S24</t>
+  </si>
+  <si>
+    <t>_23471364640</t>
+  </si>
+  <si>
+    <t>_Н.036.83.610 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 12 мм, L=610 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 12 мм, 275 бар, L=610 мм, гайка M20×1.5 S24 / гайка M20×1.5 S24</t>
+  </si>
+  <si>
+    <t>_23471364641</t>
+  </si>
+  <si>
+    <t>_Н.036.83.0810 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 12 мм, L=810 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 12 мм, 275 бар, L=810 мм, гайка M20×1.5 S24 / гайка M20×1.5 S24</t>
+  </si>
+  <si>
+    <t>_23471364642</t>
+  </si>
+  <si>
+    <t>_Н.036.83.1010 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 12 мм, L=1010 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 12 мм, 275 бар, L=1010 мм, гайка M20×1.5 S24 / гайка M20×1.5 S24</t>
+  </si>
+  <si>
+    <t>_23471364643</t>
+  </si>
+  <si>
+    <t>_Н.036.83.1110 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 12 мм, L=1110 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 12 мм, 275 бар, L=1110 мм, гайка M20×1.5 S24 / гайка M20×1.5 S24</t>
+  </si>
+  <si>
+    <t>_23471364644</t>
+  </si>
+  <si>
+    <t>_Н.036.83.1210 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 12 мм, L=1210 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 12 мм, 275 бар, L=1210 мм, гайка M20×1.5 S24 / гайка M20×1.5 S24</t>
+  </si>
+  <si>
+    <t>_23471364645</t>
+  </si>
+  <si>
+    <t>_Н.036.83.1410 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 12 мм, L=1410 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 12 мм, 275 бар, L=1410 мм, гайка M20×1.5 S24 / гайка M20×1.5 S24</t>
+  </si>
+  <si>
+    <t>_23471364646</t>
+  </si>
+  <si>
+    <t>_Н.036.83.1510 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 12 мм, L=1510 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 12 мм, 275 бар, L=1510 мм, гайка M20×1.5 S24 / гайка M20×1.5 S24</t>
+  </si>
+  <si>
+    <t>_23471364647</t>
+  </si>
+  <si>
+    <t>_Н.036.83.1610 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 12 мм, L=1610 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 12 мм, 275 бар, L=1610 мм, гайка M20×1.5 S24 / гайка M20×1.5 S24</t>
+  </si>
+  <si>
+    <t>_23471364648</t>
+  </si>
+  <si>
+    <t>_Н.036.83.1810 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 12 мм, L=1810 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 12 мм, 275 бар, L=1810 мм, гайка M20×1.5 S24 / гайка M20×1.5 S24</t>
+  </si>
+  <si>
+    <t>_23471364649</t>
+  </si>
+  <si>
+    <t>_Н.036.83.2010 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 12 мм, L=2010 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 12 мм, 275 бар, L=2010 мм, гайка M20×1.5 S24 / гайка M20×1.5 S24</t>
+  </si>
+  <si>
+    <t>_23471364650</t>
+  </si>
+  <si>
+    <t>_Н.036.83.2510 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 12 мм, L=2510 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 12 мм, 275 бар, L=2510 мм, гайка M20×1.5 S24 / гайка M20×1.5 S24</t>
+  </si>
+  <si>
+    <t>_23471364651</t>
+  </si>
+  <si>
+    <t>_Н.036.83.3010 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 12 мм, L=3010 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 12 мм, 275 бар, L=3010 мм, гайка M20×1.5 S24 / гайка M20×1.5 S24</t>
+  </si>
+  <si>
+    <t>_23471364652</t>
+  </si>
+  <si>
+    <t>_Н.036.84.0410 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 12 мм, 275 бар, L=410 мм, гайка M22×1.5 S27 / гайка M22×1.5 S27</t>
+  </si>
+  <si>
+    <t>Продуктовая семья: Соединители
+Продуктовая категория: Трубопроводы жесткие и гибкие
+Конструктивная основа: непрерывный проводящий канал
+Определённый термин: Рукав высокого давления в сборе
+Конструктивная форма и гибкость: изгибается свободно и не сохраняет форму без фиксации
+Материал основы: резина
+Рабочая среда: гидравлическая жидкость
+Размерная модель: параметрический (ID / OD / толщина стенки)
+Размер: ID 12 мм
+Сокращение в пользовательском наименовании: модифицированный
+Внутренний слой / лайнер: да
+Материал лайнера: резина NBR
+Единица продажи: шт (штучное изделие)
+Монтажная геометрия изделия: гладкий
+Профиль канала: гладкий
+Исполнение изделия: прямой
+Конструкция стенки: армированная
+Количество слоёв / слоёв армирования: 2
+Армирование: комбинированное
+Рабочее давление: 275 бар
+Температура max: 100 °C
+Стандарт / серия: 2SN
+Конструктивная расшифровка стандарта: двухслойная металлическая оплётка
+Наличие портов: с двух сторон
+Порт A: гайка M22×1.5 S27
+Порт B: гайка M22×1.5 S27</t>
+  </si>
+  <si>
+    <t>_23471364653</t>
+  </si>
+  <si>
+    <t>_Н.036.84.0610 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 12 мм, 275 бар, L=610 мм, гайка M22×1.5 S27 / гайка M22×1.5 S27</t>
+  </si>
+  <si>
+    <t>_23471364654</t>
+  </si>
+  <si>
+    <t>_Н.036.84.0810 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 12 мм, 275 бар, L=810 мм, гайка M22×1.5 S27 / гайка M22×1.5 S27</t>
+  </si>
+  <si>
+    <t>_23471364655</t>
+  </si>
+  <si>
+    <t>_Н.036.84.1010 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 12 мм, 275 бар, L=1010 мм, гайка M22×1.5 S27 / гайка M22×1.5 S27</t>
+  </si>
+  <si>
+    <t>_23471364656</t>
+  </si>
+  <si>
+    <t>_Н.036.84.1210 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 12 мм, 275 бар, L=1210 мм, гайка M22×1.5 S27 / гайка M22×1.5 S27</t>
+  </si>
+  <si>
+    <t>_23471364657</t>
+  </si>
+  <si>
+    <t>_Н.036.84.1410 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 12 мм, 275 бар, L=1410 мм, гайка M22×1.5 S27 / гайка M22×1.5 S27</t>
+  </si>
+  <si>
+    <t>_23471364658</t>
+  </si>
+  <si>
+    <t>_Н.036.84.1510 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 12 мм, 275 бар, L=1510 мм, гайка M22×1.5 S27 / гайка M22×1.5 S27</t>
+  </si>
+  <si>
+    <t>_23471364659</t>
+  </si>
+  <si>
+    <t>_Н.036.84.1610 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 12 мм, 275 бар, L=1610 мм, гайка M22×1.5 S27 / гайка M22×1.5 S27</t>
+  </si>
+  <si>
+    <t>_23471364660</t>
+  </si>
+  <si>
+    <t>_Н.036.84.2010 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 12 мм, 275 бар, L=2010 мм, гайка M22×1.5 S27 / гайка M22×1.5 S27</t>
+  </si>
+  <si>
+    <t>_23471364661</t>
+  </si>
+  <si>
+    <t>_Н.036.85.0210 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 16 мм, L=210 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 16 мм, 250 бар, L=210 мм, гайка M S32 / гайка M S32</t>
+  </si>
+  <si>
+    <t>Продуктовая семья: Соединители
+Продуктовая категория: Трубопроводы жесткие и гибкие
+Конструктивная основа: непрерывный проводящий канал
+Определённый термин: Рукав высокого давления в сборе
+Конструктивная форма и гибкость: изгибается свободно и не сохраняет форму без фиксации
+Материал основы: резина
+Рабочая среда: гидравлическая жидкость
+Размерная модель: параметрический (ID / OD / толщина стенки)
+Размер: ID 16 мм
+Сокращение в пользовательском наименовании: модифицированный
+Внутренний слой / лайнер: да
+Материал лайнера: резина NBR
+Единица продажи: шт (штучное изделие)
+Монтажная геометрия изделия: гладкий
+Профиль канала: гладкий
+Исполнение изделия: прямой
+Конструкция стенки: армированная
+Количество слоёв / слоёв армирования: 2
+Армирование: комбинированное
+Рабочее давление: 250 бар
+Температура max: 100 °C
+Стандарт / серия: 2SN
+Конструктивная расшифровка стандарта: двухслойная металлическая оплётка
+Наличие портов: с двух сторон
+Порт A: гайка M S32
+Порт B: гайка M S32</t>
+  </si>
+  <si>
+    <t>Поисковые альтернативы:
+• РВД
+• рукав ВД
+• гидравлический рукав
+• рукав 2SN
+• МБС
+• маслобензостойкий
+• рукав высокого давления ID 16 мм</t>
+  </si>
+  <si>
+    <t>_23471364662</t>
+  </si>
+  <si>
+    <t>_Н.036.85.0610 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 16 мм, L=610 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 16 мм, 250 бар, L=610 мм, гайка M S32 / гайка M S32</t>
+  </si>
+  <si>
+    <t>_23471364663</t>
+  </si>
+  <si>
+    <t>_Н.036.85.0810 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 16 мм, L=810 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 16 мм, 250 бар, L=810 мм, гайка M S32 / гайка M S32</t>
+  </si>
+  <si>
+    <t>_23471364664</t>
+  </si>
+  <si>
+    <t>_Н.036.85.1010 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 16 мм, L=1010 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 16 мм, 250 бар, L=1010 мм, гайка M S32 / гайка M S32</t>
+  </si>
+  <si>
+    <t>_23471364665</t>
+  </si>
+  <si>
+    <t>_Н.036.85.1210 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 16 мм, L=1210 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 16 мм, 250 бар, L=1210 мм, гайка M S32 / гайка M S32</t>
+  </si>
+  <si>
+    <t>_23471364666</t>
+  </si>
+  <si>
+    <t>_Н.036.85.1410 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 16 мм, L=1410 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 16 мм, 250 бар, L=1410 мм, гайка M S32 / гайка M S32</t>
+  </si>
+  <si>
+    <t>_23471364667</t>
+  </si>
+  <si>
+    <t>_Н.036.85.1510 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 16 мм, L=1510 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 16 мм, 250 бар, L=1510 мм, гайка M S32 / гайка M S32</t>
+  </si>
+  <si>
+    <t>_23471364668</t>
+  </si>
+  <si>
+    <t>_Н.036.85.1610 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 16 мм, L=1610 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 16 мм, 250 бар, L=1610 мм, гайка M S32 / гайка M S32</t>
+  </si>
+  <si>
+    <t>_23471364669</t>
+  </si>
+  <si>
+    <t>_Н.036.85.1810 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 16 мм, L=1810 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 16 мм, 250 бар, L=1810 мм, гайка M S32 / гайка M S32</t>
+  </si>
+  <si>
+    <t>_23471364670</t>
+  </si>
+  <si>
+    <t>_Н.036.85.2010 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 16 мм, L=2010 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 16 мм, 250 бар, L=2010 мм, гайка M S32 / гайка M S32</t>
+  </si>
+  <si>
+    <t>_23471364671</t>
+  </si>
+  <si>
+    <t>_Н.036.87.1010 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 19 мм, L=1010 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 19 мм, 215 бар, L=1010 мм, гайка M S41 / гайка M S41</t>
+  </si>
+  <si>
+    <t>Продуктовая семья: Соединители
+Продуктовая категория: Трубопроводы жесткие и гибкие
+Конструктивная основа: непрерывный проводящий канал
+Определённый термин: Рукав высокого давления в сборе
+Конструктивная форма и гибкость: изгибается свободно и не сохраняет форму без фиксации
+Материал основы: резина
+Рабочая среда: гидравлическая жидкость
+Размерная модель: параметрический (ID / OD / толщина стенки)
+Размер: ID 19 мм
+Сокращение в пользовательском наименовании: модифицированный
+Внутренний слой / лайнер: да
+Материал лайнера: резина NBR
+Единица продажи: шт (штучное изделие)
+Монтажная геометрия изделия: гладкий
+Профиль канала: гладкий
+Исполнение изделия: прямой
+Конструкция стенки: армированная
+Количество слоёв / слоёв армирования: 2
+Армирование: комбинированное
+Рабочее давление: 215 бар
+Температура max: 100 °C
+Стандарт / серия: 2SN
+Конструктивная расшифровка стандарта: двухслойная металлическая оплётка
+Наличие портов: с двух сторон
+Порт A: гайка M S41
+Порт B: гайка M S41</t>
+  </si>
+  <si>
+    <t>Поисковые альтернативы:
+• РВД
+• рукав ВД
+• гидравлический рукав
+• рукав 2SN
+• МБС
+• маслобензостойкий
+• рукав высокого давления ID 19 мм</t>
+  </si>
+  <si>
+    <t>_23471364672</t>
+  </si>
+  <si>
+    <t>_Н.036.87.1210 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 20 мм, L=1210 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 20 мм, 215 бар, L=1210 мм, гайка M S41 / гайка M S41</t>
+  </si>
+  <si>
+    <t>Продуктовая семья: Соединители
+Продуктовая категория: Трубопроводы жесткие и гибкие
+Конструктивная основа: непрерывный проводящий канал
+Определённый термин: Рукав высокого давления в сборе
+Конструктивная форма и гибкость: изгибается свободно и не сохраняет форму без фиксации
+Материал основы: резина
+Рабочая среда: гидравлическая жидкость
+Размерная модель: параметрический (ID / OD / толщина стенки)
+Размер: ID 20 мм
+Сокращение в пользовательском наименовании: модифицированный
+Внутренний слой / лайнер: да
+Материал лайнера: резина NBR
+Единица продажи: шт (штучное изделие)
+Монтажная геометрия изделия: гладкий
+Профиль канала: гладкий
+Исполнение изделия: прямой
+Конструкция стенки: армированная
+Количество слоёв / слоёв армирования: 2
+Армирование: комбинированное
+Рабочее давление: 215 бар
+Температура max: 100 °C
+Стандарт / серия: 2SN
+Конструктивная расшифровка стандарта: двухслойная металлическая оплётка
+Наличие портов: с двух сторон
+Порт A: гайка M S41
+Порт B: гайка M S41</t>
+  </si>
+  <si>
+    <t>Поисковые альтернативы:
+• РВД
+• рукав ВД
+• гидравлический рукав
+• рукав 2SN
+• МБС
+• маслобензостойкий
+• рукав высокого давления ID 20 мм</t>
+  </si>
+  <si>
+    <t>_23471364673</t>
+  </si>
+  <si>
+    <t>_Н.036.87.1510 2SN</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 20 мм, L=1510 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 20 мм, 215 бар, L=1510 мм, гайка M S41 / гайка M S41</t>
+  </si>
+  <si>
+    <t>_23471364674</t>
+  </si>
+  <si>
+    <t>_680-4607140-100</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 10 мм, L=1000 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 10 мм, L=1000 мм, гайка M20×1.5 S24 / гайка M20×1.5 S24 90°</t>
+  </si>
+  <si>
+    <t>Продуктовая семья: Соединители
+Продуктовая категория: Трубопроводы жесткие и гибкие
+Конструктивная основа: непрерывный проводящий канал
+Определённый термин: Рукав высокого давления в сборе
+Конструктивная форма и гибкость: изгибается свободно и не сохраняет форму без фиксации
+Материал основы: резина
+Рабочая среда: гидравлическая жидкость
+Размерная модель: параметрический (ID / OD / толщина стенки)
+Размер: ID 10 мм
+Сокращение в пользовательском наименовании: модифицированный
+Внутренний слой / лайнер: да
+Материал лайнера: резина NBR
+Единица продажи: шт (штучное изделие)
+Монтажная геометрия изделия: гладкий
+Профиль канала: гладкий
+Исполнение изделия: прямой
+Конструкция стенки: армированная
+Количество слоёв / слоёв армирования: 2
+Армирование: комбинированное
+Температура max: 100 °C
+Стандарт / серия: 2SN
+Конструктивная расшифровка стандарта: двухслойная металлическая оплётка
+Наличие портов: с двух сторон
+Порт A: гайка M20×1.5 S24
+Порт B: гайка M20×1.5 S24 90°</t>
+  </si>
+  <si>
+    <t>_23471364675</t>
+  </si>
+  <si>
+    <t>_680-4607140-120</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 10 мм, L=1200 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 10 мм, L=1200 мм, гайка M20×1.5 S24 / гайка M20×1.5 S24 90°</t>
+  </si>
+  <si>
+    <t>_23471364676</t>
+  </si>
+  <si>
+    <t>_680-4607140-150</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 10 мм, L=1500 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 10 мм, L=1500 мм, гайка M20×1.5 S24 / гайка M20×1.5 S24 90°</t>
+  </si>
+  <si>
+    <t>_23471364677</t>
+  </si>
+  <si>
+    <t>_680-4607140-180</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 10 мм, L=1800 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 10 мм, L=1800 мм, гайка M20×1.5 S24 / гайка M20×1.5 S24 90°</t>
+  </si>
+  <si>
+    <t>_2347798889</t>
+  </si>
+  <si>
+    <t>_680-4607140-01</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 10 мм, L=420 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 10 мм, L=420 мм, гайка M20×1.5 S24 / гайка M20×1.5 S24 90°</t>
+  </si>
+  <si>
+    <t>_2347798890</t>
+  </si>
+  <si>
+    <t>_680-4607140-04</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 10 мм, L=600 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 10 мм, L=600 мм, гайка M20×1.5 S24 / гайка M20×1.5 S24 90°</t>
+  </si>
+  <si>
+    <t>_2347798891</t>
+  </si>
+  <si>
+    <t>_680-4607140-06</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе резиновый модифицированный 2SN ID 10 мм, L=800 мм</t>
+  </si>
+  <si>
+    <t>Рукав высокого давления в сборе МБС резиновый 2-слойно-армированный комбинированно-армированный с лайнером резина NBR 2SN ID 10 мм, L=800 мм, гайка M20×1.5 S24 / гайка M20×1.5 S24 90°</t>
+  </si>
+  <si>
+    <t>гидравлическая жидкость</t>
+  </si>
+  <si>
+    <t>EN 853 1SN</t>
+  </si>
+  <si>
+    <t>EN 853 2SN</t>
+  </si>
+  <si>
+    <t>Резьба</t>
+  </si>
+  <si>
+    <t>Грань</t>
+  </si>
+  <si>
+    <t>M22×1.5</t>
+  </si>
+  <si>
+    <t>M27×1.5</t>
+  </si>
+  <si>
+    <t>M33×2.0</t>
+  </si>
+  <si>
+    <t>M16×1.5</t>
+  </si>
+  <si>
+    <t>S19</t>
+  </si>
+  <si>
+    <t>M18×1.5</t>
+  </si>
+  <si>
+    <t>S22</t>
+  </si>
+  <si>
+    <t>M20×1.5</t>
+  </si>
+  <si>
+    <t>S24</t>
+  </si>
+  <si>
+    <t>S27</t>
+  </si>
+  <si>
+    <t>S32</t>
+  </si>
+  <si>
+    <t>S41</t>
   </si>
 </sst>
 </file>
@@ -6904,7 +8528,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T166"/>
+  <dimension ref="A1:V262"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="18" customWidth="1"/>
@@ -6913,7 +8537,7 @@
     <col min="8" max="8" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="90" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6971,11 +8595,17 @@
       <c r="S1" s="1" t="s">
         <v>905</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="T1" s="1" t="s">
+        <v>1395</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>1396</v>
+      </c>
+      <c r="V1" s="4" t="s">
         <v>997</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
@@ -7031,11 +8661,13 @@
       <c r="S2" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T2">
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+      <c r="V2">
         <v>190</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
@@ -7091,11 +8723,13 @@
       <c r="S3" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T3">
+      <c r="T3" s="3"/>
+      <c r="U3" s="3"/>
+      <c r="V3">
         <v>190</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
@@ -7151,11 +8785,13 @@
       <c r="S4" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T4">
+      <c r="T4" s="3"/>
+      <c r="U4" s="3"/>
+      <c r="V4">
         <v>190</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>22</v>
       </c>
@@ -7211,11 +8847,13 @@
       <c r="S5" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T5">
+      <c r="T5" s="3"/>
+      <c r="U5" s="3"/>
+      <c r="V5">
         <v>191</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>27</v>
       </c>
@@ -7271,11 +8909,13 @@
       <c r="S6" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T6">
+      <c r="T6" s="3"/>
+      <c r="U6" s="3"/>
+      <c r="V6">
         <v>191</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>30</v>
       </c>
@@ -7331,11 +8971,13 @@
       <c r="S7" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T7">
+      <c r="T7" s="3"/>
+      <c r="U7" s="3"/>
+      <c r="V7">
         <v>191</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>35</v>
       </c>
@@ -7391,11 +9033,13 @@
       <c r="S8" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T8">
+      <c r="T8" s="3"/>
+      <c r="U8" s="3"/>
+      <c r="V8">
         <v>191</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>38</v>
       </c>
@@ -7451,11 +9095,13 @@
       <c r="S9" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T9">
+      <c r="T9" s="3"/>
+      <c r="U9" s="3"/>
+      <c r="V9">
         <v>192</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>43</v>
       </c>
@@ -7511,11 +9157,13 @@
       <c r="S10" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T10">
+      <c r="T10" s="3"/>
+      <c r="U10" s="3"/>
+      <c r="V10">
         <v>192</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>48</v>
       </c>
@@ -7571,11 +9219,13 @@
       <c r="S11" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T11">
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+      <c r="V11">
         <v>192</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>53</v>
       </c>
@@ -7631,11 +9281,13 @@
       <c r="S12" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T12">
+      <c r="T12" s="3"/>
+      <c r="U12" s="3"/>
+      <c r="V12">
         <v>192</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>58</v>
       </c>
@@ -7691,11 +9343,13 @@
       <c r="S13" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T13">
+      <c r="T13" s="3"/>
+      <c r="U13" s="3"/>
+      <c r="V13">
         <v>192</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>63</v>
       </c>
@@ -7751,11 +9405,13 @@
       <c r="S14" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T14">
+      <c r="T14" s="3"/>
+      <c r="U14" s="3"/>
+      <c r="V14">
         <v>192</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>68</v>
       </c>
@@ -7811,11 +9467,13 @@
       <c r="S15" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T15">
+      <c r="T15" s="3"/>
+      <c r="U15" s="3"/>
+      <c r="V15">
         <v>192</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>73</v>
       </c>
@@ -7871,11 +9529,13 @@
       <c r="S16" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T16">
+      <c r="T16" s="3"/>
+      <c r="U16" s="3"/>
+      <c r="V16">
         <v>192</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>78</v>
       </c>
@@ -7931,11 +9591,13 @@
       <c r="S17" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T17">
+      <c r="T17" s="3"/>
+      <c r="U17" s="3"/>
+      <c r="V17">
         <v>192</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>83</v>
       </c>
@@ -7991,11 +9653,13 @@
       <c r="S18" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T18">
+      <c r="T18" s="3"/>
+      <c r="U18" s="3"/>
+      <c r="V18">
         <v>192</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>88</v>
       </c>
@@ -8051,11 +9715,13 @@
       <c r="S19" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T19">
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+      <c r="V19">
         <v>192</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>93</v>
       </c>
@@ -8111,11 +9777,13 @@
       <c r="S20" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T20">
+      <c r="T20" s="3"/>
+      <c r="U20" s="3"/>
+      <c r="V20">
         <v>192</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>98</v>
       </c>
@@ -8171,11 +9839,13 @@
       <c r="S21" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T21">
+      <c r="T21" s="3"/>
+      <c r="U21" s="3"/>
+      <c r="V21">
         <v>192</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>103</v>
       </c>
@@ -8231,11 +9901,13 @@
       <c r="S22" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T22">
+      <c r="T22" s="3"/>
+      <c r="U22" s="3"/>
+      <c r="V22">
         <v>192</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>108</v>
       </c>
@@ -8291,11 +9963,13 @@
       <c r="S23" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T23">
+      <c r="T23" s="3"/>
+      <c r="U23" s="3"/>
+      <c r="V23">
         <v>192</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>113</v>
       </c>
@@ -8351,11 +10025,13 @@
       <c r="S24" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T24">
+      <c r="T24" s="3"/>
+      <c r="U24" s="3"/>
+      <c r="V24">
         <v>192</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>118</v>
       </c>
@@ -8411,11 +10087,13 @@
       <c r="S25" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T25">
+      <c r="T25" s="3"/>
+      <c r="U25" s="3"/>
+      <c r="V25">
         <v>192</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>123</v>
       </c>
@@ -8471,11 +10149,13 @@
       <c r="S26" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T26">
+      <c r="T26" s="3"/>
+      <c r="U26" s="3"/>
+      <c r="V26">
         <v>192</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>128</v>
       </c>
@@ -8531,11 +10211,13 @@
       <c r="S27" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T27">
+      <c r="T27" s="3"/>
+      <c r="U27" s="3"/>
+      <c r="V27">
         <v>192</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>133</v>
       </c>
@@ -8591,11 +10273,13 @@
       <c r="S28" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T28">
+      <c r="T28" s="3"/>
+      <c r="U28" s="3"/>
+      <c r="V28">
         <v>192</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>137</v>
       </c>
@@ -8651,11 +10335,13 @@
       <c r="S29" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T29">
+      <c r="T29" s="3"/>
+      <c r="U29" s="3"/>
+      <c r="V29">
         <v>192</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>141</v>
       </c>
@@ -8711,11 +10397,13 @@
       <c r="S30" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T30">
+      <c r="T30" s="3"/>
+      <c r="U30" s="3"/>
+      <c r="V30">
         <v>192</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>145</v>
       </c>
@@ -8771,11 +10459,13 @@
       <c r="S31" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T31">
+      <c r="T31" s="3"/>
+      <c r="U31" s="3"/>
+      <c r="V31">
         <v>192</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>149</v>
       </c>
@@ -8831,11 +10521,13 @@
       <c r="S32" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T32">
+      <c r="T32" s="3"/>
+      <c r="U32" s="3"/>
+      <c r="V32">
         <v>192</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>153</v>
       </c>
@@ -8891,11 +10583,13 @@
       <c r="S33" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T33">
+      <c r="T33" s="3"/>
+      <c r="U33" s="3"/>
+      <c r="V33">
         <v>192</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>157</v>
       </c>
@@ -8951,11 +10645,13 @@
       <c r="S34" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T34">
+      <c r="T34" s="3"/>
+      <c r="U34" s="3"/>
+      <c r="V34">
         <v>192</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>161</v>
       </c>
@@ -9011,11 +10707,13 @@
       <c r="S35" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T35">
+      <c r="T35" s="3"/>
+      <c r="U35" s="3"/>
+      <c r="V35">
         <v>192</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>165</v>
       </c>
@@ -9071,11 +10769,13 @@
       <c r="S36" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T36">
+      <c r="T36" s="3"/>
+      <c r="U36" s="3"/>
+      <c r="V36">
         <v>192</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>169</v>
       </c>
@@ -9131,11 +10831,13 @@
       <c r="S37" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T37">
+      <c r="T37" s="3"/>
+      <c r="U37" s="3"/>
+      <c r="V37">
         <v>192</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>173</v>
       </c>
@@ -9191,11 +10893,13 @@
       <c r="S38" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T38">
+      <c r="T38" s="3"/>
+      <c r="U38" s="3"/>
+      <c r="V38">
         <v>192</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>177</v>
       </c>
@@ -9251,11 +10955,13 @@
       <c r="S39" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T39">
+      <c r="T39" s="3"/>
+      <c r="U39" s="3"/>
+      <c r="V39">
         <v>192</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>181</v>
       </c>
@@ -9311,11 +11017,13 @@
       <c r="S40" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T40">
+      <c r="T40" s="3"/>
+      <c r="U40" s="3"/>
+      <c r="V40">
         <v>192</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>185</v>
       </c>
@@ -9371,11 +11079,13 @@
       <c r="S41" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T41">
+      <c r="T41" s="3"/>
+      <c r="U41" s="3"/>
+      <c r="V41">
         <v>192</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>189</v>
       </c>
@@ -9431,11 +11141,13 @@
       <c r="S42" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T42">
+      <c r="T42" s="3"/>
+      <c r="U42" s="3"/>
+      <c r="V42">
         <v>192</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>193</v>
       </c>
@@ -9491,11 +11203,13 @@
       <c r="S43" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T43">
+      <c r="T43" s="3"/>
+      <c r="U43" s="3"/>
+      <c r="V43">
         <v>192</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>197</v>
       </c>
@@ -9551,11 +11265,13 @@
       <c r="S44" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T44">
+      <c r="T44" s="3"/>
+      <c r="U44" s="3"/>
+      <c r="V44">
         <v>192</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>201</v>
       </c>
@@ -9611,11 +11327,13 @@
       <c r="S45" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T45">
+      <c r="T45" s="3"/>
+      <c r="U45" s="3"/>
+      <c r="V45">
         <v>192</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>205</v>
       </c>
@@ -9671,11 +11389,13 @@
       <c r="S46" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T46">
+      <c r="T46" s="3"/>
+      <c r="U46" s="3"/>
+      <c r="V46">
         <v>192</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>209</v>
       </c>
@@ -9729,11 +11449,13 @@
       <c r="S47" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T47">
+      <c r="T47" s="3"/>
+      <c r="U47" s="3"/>
+      <c r="V47">
         <v>193</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>213</v>
       </c>
@@ -9787,11 +11509,13 @@
       <c r="S48" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T48">
+      <c r="T48" s="3"/>
+      <c r="U48" s="3"/>
+      <c r="V48">
         <v>193</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>217</v>
       </c>
@@ -9845,11 +11569,13 @@
       <c r="S49" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T49">
+      <c r="T49" s="3"/>
+      <c r="U49" s="3"/>
+      <c r="V49">
         <v>193</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>221</v>
       </c>
@@ -9903,11 +11629,13 @@
       <c r="S50" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T50">
+      <c r="T50" s="3"/>
+      <c r="U50" s="3"/>
+      <c r="V50">
         <v>193</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>225</v>
       </c>
@@ -9961,11 +11689,13 @@
       <c r="S51" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T51">
+      <c r="T51" s="3"/>
+      <c r="U51" s="3"/>
+      <c r="V51">
         <v>193</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>229</v>
       </c>
@@ -10019,11 +11749,13 @@
       <c r="S52" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T52">
+      <c r="T52" s="3"/>
+      <c r="U52" s="3"/>
+      <c r="V52">
         <v>193</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>233</v>
       </c>
@@ -10077,11 +11809,13 @@
       <c r="S53" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T53">
+      <c r="T53" s="3"/>
+      <c r="U53" s="3"/>
+      <c r="V53">
         <v>194</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>238</v>
       </c>
@@ -10135,11 +11869,13 @@
       <c r="S54" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T54">
+      <c r="T54" s="3"/>
+      <c r="U54" s="3"/>
+      <c r="V54">
         <v>194</v>
       </c>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>243</v>
       </c>
@@ -10193,11 +11929,13 @@
       <c r="S55" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T55">
+      <c r="T55" s="3"/>
+      <c r="U55" s="3"/>
+      <c r="V55">
         <v>194</v>
       </c>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>248</v>
       </c>
@@ -10251,11 +11989,13 @@
       <c r="S56" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T56">
+      <c r="T56" s="3"/>
+      <c r="U56" s="3"/>
+      <c r="V56">
         <v>194</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>253</v>
       </c>
@@ -10309,11 +12049,13 @@
       <c r="S57" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T57">
+      <c r="T57" s="3"/>
+      <c r="U57" s="3"/>
+      <c r="V57">
         <v>194</v>
       </c>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>258</v>
       </c>
@@ -10367,11 +12109,13 @@
       <c r="S58" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T58">
+      <c r="T58" s="3"/>
+      <c r="U58" s="3"/>
+      <c r="V58">
         <v>195</v>
       </c>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>262</v>
       </c>
@@ -10425,11 +12169,13 @@
       <c r="S59" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T59">
+      <c r="T59" s="3"/>
+      <c r="U59" s="3"/>
+      <c r="V59">
         <v>196</v>
       </c>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>266</v>
       </c>
@@ -10483,11 +12229,13 @@
       <c r="S60" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T60">
+      <c r="T60" s="3"/>
+      <c r="U60" s="3"/>
+      <c r="V60">
         <v>196</v>
       </c>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>270</v>
       </c>
@@ -10541,11 +12289,13 @@
       <c r="S61" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T61">
+      <c r="T61" s="3"/>
+      <c r="U61" s="3"/>
+      <c r="V61">
         <v>196</v>
       </c>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>274</v>
       </c>
@@ -10599,11 +12349,13 @@
       <c r="S62" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T62">
+      <c r="T62" s="3"/>
+      <c r="U62" s="3"/>
+      <c r="V62">
         <v>196</v>
       </c>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>278</v>
       </c>
@@ -10657,11 +12409,13 @@
       <c r="S63" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T63">
+      <c r="T63" s="3"/>
+      <c r="U63" s="3"/>
+      <c r="V63">
         <v>196</v>
       </c>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>282</v>
       </c>
@@ -10715,11 +12469,13 @@
       <c r="S64" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T64">
+      <c r="T64" s="3"/>
+      <c r="U64" s="3"/>
+      <c r="V64">
         <v>196</v>
       </c>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>286</v>
       </c>
@@ -10773,11 +12529,13 @@
       <c r="S65" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T65">
+      <c r="T65" s="3"/>
+      <c r="U65" s="3"/>
+      <c r="V65">
         <v>197</v>
       </c>
     </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>291</v>
       </c>
@@ -10831,11 +12589,13 @@
       <c r="S66" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T66">
+      <c r="T66" s="3"/>
+      <c r="U66" s="3"/>
+      <c r="V66">
         <v>197</v>
       </c>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>296</v>
       </c>
@@ -10889,11 +12649,13 @@
       <c r="S67" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T67">
+      <c r="T67" s="3"/>
+      <c r="U67" s="3"/>
+      <c r="V67">
         <v>197</v>
       </c>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>301</v>
       </c>
@@ -10947,11 +12709,13 @@
       <c r="S68" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T68">
+      <c r="T68" s="3"/>
+      <c r="U68" s="3"/>
+      <c r="V68">
         <v>197</v>
       </c>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>306</v>
       </c>
@@ -11005,11 +12769,13 @@
       <c r="S69" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T69">
+      <c r="T69" s="3"/>
+      <c r="U69" s="3"/>
+      <c r="V69">
         <v>197</v>
       </c>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>311</v>
       </c>
@@ -11063,11 +12829,13 @@
       <c r="S70" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T70">
+      <c r="T70" s="3"/>
+      <c r="U70" s="3"/>
+      <c r="V70">
         <v>197</v>
       </c>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>316</v>
       </c>
@@ -11121,11 +12889,13 @@
       <c r="S71" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T71">
+      <c r="T71" s="3"/>
+      <c r="U71" s="3"/>
+      <c r="V71">
         <v>197</v>
       </c>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>320</v>
       </c>
@@ -11179,11 +12949,13 @@
       <c r="S72" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T72">
+      <c r="T72" s="3"/>
+      <c r="U72" s="3"/>
+      <c r="V72">
         <v>197</v>
       </c>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>325</v>
       </c>
@@ -11237,11 +13009,13 @@
       <c r="S73" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T73">
+      <c r="T73" s="3"/>
+      <c r="U73" s="3"/>
+      <c r="V73">
         <v>197</v>
       </c>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>329</v>
       </c>
@@ -11295,11 +13069,13 @@
       <c r="S74" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T74">
+      <c r="T74" s="3"/>
+      <c r="U74" s="3"/>
+      <c r="V74">
         <v>197</v>
       </c>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>334</v>
       </c>
@@ -11353,11 +13129,13 @@
       <c r="S75" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T75">
+      <c r="T75" s="3"/>
+      <c r="U75" s="3"/>
+      <c r="V75">
         <v>197</v>
       </c>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>338</v>
       </c>
@@ -11411,11 +13189,13 @@
       <c r="S76" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T76">
+      <c r="T76" s="3"/>
+      <c r="U76" s="3"/>
+      <c r="V76">
         <v>197</v>
       </c>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>343</v>
       </c>
@@ -11469,11 +13249,13 @@
       <c r="S77" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T77">
+      <c r="T77" s="3"/>
+      <c r="U77" s="3"/>
+      <c r="V77">
         <v>197</v>
       </c>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>347</v>
       </c>
@@ -11527,11 +13309,13 @@
       <c r="S78" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T78">
+      <c r="T78" s="3"/>
+      <c r="U78" s="3"/>
+      <c r="V78">
         <v>197</v>
       </c>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>351</v>
       </c>
@@ -11585,11 +13369,13 @@
       <c r="S79" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T79">
+      <c r="T79" s="3"/>
+      <c r="U79" s="3"/>
+      <c r="V79">
         <v>197</v>
       </c>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>356</v>
       </c>
@@ -11643,11 +13429,13 @@
       <c r="S80" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T80">
+      <c r="T80" s="3"/>
+      <c r="U80" s="3"/>
+      <c r="V80">
         <v>197</v>
       </c>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>361</v>
       </c>
@@ -11701,11 +13489,13 @@
       <c r="S81" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T81">
+      <c r="T81" s="3"/>
+      <c r="U81" s="3"/>
+      <c r="V81">
         <v>197</v>
       </c>
     </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>365</v>
       </c>
@@ -11759,11 +13549,13 @@
       <c r="S82" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T82">
+      <c r="T82" s="3"/>
+      <c r="U82" s="3"/>
+      <c r="V82">
         <v>197</v>
       </c>
     </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>370</v>
       </c>
@@ -11817,11 +13609,13 @@
       <c r="S83" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T83">
+      <c r="T83" s="3"/>
+      <c r="U83" s="3"/>
+      <c r="V83">
         <v>197</v>
       </c>
     </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>374</v>
       </c>
@@ -11875,11 +13669,13 @@
       <c r="S84" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T84">
+      <c r="T84" s="3"/>
+      <c r="U84" s="3"/>
+      <c r="V84">
         <v>197</v>
       </c>
     </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>379</v>
       </c>
@@ -11933,11 +13729,13 @@
       <c r="S85" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T85">
+      <c r="T85" s="3"/>
+      <c r="U85" s="3"/>
+      <c r="V85">
         <v>197</v>
       </c>
     </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>384</v>
       </c>
@@ -11991,11 +13789,13 @@
       <c r="S86" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T86">
+      <c r="T86" s="3"/>
+      <c r="U86" s="3"/>
+      <c r="V86">
         <v>197</v>
       </c>
     </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>389</v>
       </c>
@@ -12049,11 +13849,13 @@
       <c r="S87" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T87">
+      <c r="T87" s="3"/>
+      <c r="U87" s="3"/>
+      <c r="V87">
         <v>197</v>
       </c>
     </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>394</v>
       </c>
@@ -12107,11 +13909,13 @@
       <c r="S88" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T88">
+      <c r="T88" s="3"/>
+      <c r="U88" s="3"/>
+      <c r="V88">
         <v>198</v>
       </c>
     </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>398</v>
       </c>
@@ -12165,11 +13969,13 @@
       <c r="S89" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T89">
+      <c r="T89" s="3"/>
+      <c r="U89" s="3"/>
+      <c r="V89">
         <v>198</v>
       </c>
     </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>402</v>
       </c>
@@ -12223,11 +14029,13 @@
       <c r="S90" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T90">
+      <c r="T90" s="3"/>
+      <c r="U90" s="3"/>
+      <c r="V90">
         <v>198</v>
       </c>
     </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>406</v>
       </c>
@@ -12281,11 +14089,13 @@
       <c r="S91" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T91">
+      <c r="T91" s="3"/>
+      <c r="U91" s="3"/>
+      <c r="V91">
         <v>198</v>
       </c>
     </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>410</v>
       </c>
@@ -12339,11 +14149,13 @@
       <c r="S92" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T92">
+      <c r="T92" s="3"/>
+      <c r="U92" s="3"/>
+      <c r="V92">
         <v>199</v>
       </c>
     </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>414</v>
       </c>
@@ -12397,11 +14209,13 @@
       <c r="S93" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T93">
+      <c r="T93" s="3"/>
+      <c r="U93" s="3"/>
+      <c r="V93">
         <v>199</v>
       </c>
     </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>419</v>
       </c>
@@ -12455,11 +14269,13 @@
       <c r="S94" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T94">
+      <c r="T94" s="3"/>
+      <c r="U94" s="3"/>
+      <c r="V94">
         <v>199</v>
       </c>
     </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>423</v>
       </c>
@@ -12513,11 +14329,13 @@
       <c r="S95" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T95">
+      <c r="T95" s="3"/>
+      <c r="U95" s="3"/>
+      <c r="V95">
         <v>199</v>
       </c>
     </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>428</v>
       </c>
@@ -12571,11 +14389,13 @@
       <c r="S96" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T96">
+      <c r="T96" s="3"/>
+      <c r="U96" s="3"/>
+      <c r="V96">
         <v>199</v>
       </c>
     </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>433</v>
       </c>
@@ -12629,11 +14449,13 @@
       <c r="S97" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T97">
+      <c r="T97" s="3"/>
+      <c r="U97" s="3"/>
+      <c r="V97">
         <v>199</v>
       </c>
     </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>438</v>
       </c>
@@ -12687,11 +14509,13 @@
       <c r="S98" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T98">
+      <c r="T98" s="3"/>
+      <c r="U98" s="3"/>
+      <c r="V98">
         <v>200</v>
       </c>
     </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>442</v>
       </c>
@@ -12745,11 +14569,13 @@
       <c r="S99" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T99">
+      <c r="T99" s="3"/>
+      <c r="U99" s="3"/>
+      <c r="V99">
         <v>200</v>
       </c>
     </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>446</v>
       </c>
@@ -12803,11 +14629,13 @@
       <c r="S100" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T100">
+      <c r="T100" s="3"/>
+      <c r="U100" s="3"/>
+      <c r="V100">
         <v>200</v>
       </c>
     </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>450</v>
       </c>
@@ -12861,11 +14689,13 @@
       <c r="S101" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T101">
+      <c r="T101" s="3"/>
+      <c r="U101" s="3"/>
+      <c r="V101">
         <v>200</v>
       </c>
     </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>454</v>
       </c>
@@ -12919,11 +14749,13 @@
       <c r="S102" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T102">
+      <c r="T102" s="3"/>
+      <c r="U102" s="3"/>
+      <c r="V102">
         <v>200</v>
       </c>
     </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>458</v>
       </c>
@@ -12977,11 +14809,13 @@
       <c r="S103" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T103">
+      <c r="T103" s="3"/>
+      <c r="U103" s="3"/>
+      <c r="V103">
         <v>200</v>
       </c>
     </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>462</v>
       </c>
@@ -13033,11 +14867,13 @@
       <c r="S104" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T104">
+      <c r="T104" s="3"/>
+      <c r="U104" s="3"/>
+      <c r="V104">
         <v>201</v>
       </c>
     </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>468</v>
       </c>
@@ -13089,11 +14925,13 @@
       <c r="S105" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T105">
+      <c r="T105" s="3"/>
+      <c r="U105" s="3"/>
+      <c r="V105">
         <v>201</v>
       </c>
     </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>474</v>
       </c>
@@ -13145,11 +14983,13 @@
       <c r="S106" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T106">
+      <c r="T106" s="3"/>
+      <c r="U106" s="3"/>
+      <c r="V106">
         <v>201</v>
       </c>
     </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>480</v>
       </c>
@@ -13201,11 +15041,13 @@
       <c r="S107" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T107">
+      <c r="T107" s="3"/>
+      <c r="U107" s="3"/>
+      <c r="V107">
         <v>201</v>
       </c>
     </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>486</v>
       </c>
@@ -13257,11 +15099,13 @@
       <c r="S108" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T108">
+      <c r="T108" s="3"/>
+      <c r="U108" s="3"/>
+      <c r="V108">
         <v>201</v>
       </c>
     </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>492</v>
       </c>
@@ -13313,11 +15157,13 @@
       <c r="S109" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T109">
+      <c r="T109" s="3"/>
+      <c r="U109" s="3"/>
+      <c r="V109">
         <v>201</v>
       </c>
     </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>498</v>
       </c>
@@ -13369,11 +15215,13 @@
       <c r="S110" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T110">
+      <c r="T110" s="3"/>
+      <c r="U110" s="3"/>
+      <c r="V110">
         <v>201</v>
       </c>
     </row>
-    <row r="111" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>504</v>
       </c>
@@ -13425,11 +15273,13 @@
       <c r="S111" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T111">
+      <c r="T111" s="3"/>
+      <c r="U111" s="3"/>
+      <c r="V111">
         <v>201</v>
       </c>
     </row>
-    <row r="112" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>510</v>
       </c>
@@ -13481,11 +15331,13 @@
       <c r="S112" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T112">
+      <c r="T112" s="3"/>
+      <c r="U112" s="3"/>
+      <c r="V112">
         <v>201</v>
       </c>
     </row>
-    <row r="113" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>516</v>
       </c>
@@ -13537,11 +15389,13 @@
       <c r="S113" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T113">
+      <c r="T113" s="3"/>
+      <c r="U113" s="3"/>
+      <c r="V113">
         <v>201</v>
       </c>
     </row>
-    <row r="114" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>522</v>
       </c>
@@ -13593,11 +15447,13 @@
       <c r="S114" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T114">
+      <c r="T114" s="3"/>
+      <c r="U114" s="3"/>
+      <c r="V114">
         <v>201</v>
       </c>
     </row>
-    <row r="115" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>528</v>
       </c>
@@ -13651,11 +15507,13 @@
       <c r="S115" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T115">
+      <c r="T115" s="3"/>
+      <c r="U115" s="3"/>
+      <c r="V115">
         <v>202</v>
       </c>
     </row>
-    <row r="116" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>533</v>
       </c>
@@ -13703,11 +15561,13 @@
       <c r="S116" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T116">
+      <c r="T116" s="3"/>
+      <c r="U116" s="3"/>
+      <c r="V116">
         <v>202</v>
       </c>
     </row>
-    <row r="117" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>539</v>
       </c>
@@ -13755,11 +15615,13 @@
       <c r="S117" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T117">
+      <c r="T117" s="3"/>
+      <c r="U117" s="3"/>
+      <c r="V117">
         <v>202</v>
       </c>
     </row>
-    <row r="118" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>545</v>
       </c>
@@ -13807,11 +15669,13 @@
       <c r="S118" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T118">
+      <c r="T118" s="3"/>
+      <c r="U118" s="3"/>
+      <c r="V118">
         <v>202</v>
       </c>
     </row>
-    <row r="119" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>551</v>
       </c>
@@ -13859,11 +15723,13 @@
       <c r="S119" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T119">
+      <c r="T119" s="3"/>
+      <c r="U119" s="3"/>
+      <c r="V119">
         <v>202</v>
       </c>
     </row>
-    <row r="120" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>557</v>
       </c>
@@ -13911,11 +15777,13 @@
       <c r="S120" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T120">
+      <c r="T120" s="3"/>
+      <c r="U120" s="3"/>
+      <c r="V120">
         <v>202</v>
       </c>
     </row>
-    <row r="121" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>563</v>
       </c>
@@ -13963,11 +15831,13 @@
       <c r="S121" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T121">
+      <c r="T121" s="3"/>
+      <c r="U121" s="3"/>
+      <c r="V121">
         <v>203</v>
       </c>
     </row>
-    <row r="122" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>569</v>
       </c>
@@ -14015,11 +15885,13 @@
       <c r="S122" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T122">
+      <c r="T122" s="3"/>
+      <c r="U122" s="3"/>
+      <c r="V122">
         <v>203</v>
       </c>
     </row>
-    <row r="123" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>575</v>
       </c>
@@ -14067,11 +15939,13 @@
       <c r="S123" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T123">
+      <c r="T123" s="3"/>
+      <c r="U123" s="3"/>
+      <c r="V123">
         <v>203</v>
       </c>
     </row>
-    <row r="124" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>581</v>
       </c>
@@ -14119,11 +15993,13 @@
       <c r="S124" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T124">
+      <c r="T124" s="3"/>
+      <c r="U124" s="3"/>
+      <c r="V124">
         <v>203</v>
       </c>
     </row>
-    <row r="125" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>586</v>
       </c>
@@ -14171,11 +16047,13 @@
       <c r="S125" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T125">
+      <c r="T125" s="3"/>
+      <c r="U125" s="3"/>
+      <c r="V125">
         <v>203</v>
       </c>
     </row>
-    <row r="126" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>591</v>
       </c>
@@ -14223,11 +16101,13 @@
       <c r="S126" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T126">
+      <c r="T126" s="3"/>
+      <c r="U126" s="3"/>
+      <c r="V126">
         <v>203</v>
       </c>
     </row>
-    <row r="127" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>596</v>
       </c>
@@ -14275,11 +16155,13 @@
       <c r="S127" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T127">
+      <c r="T127" s="3"/>
+      <c r="U127" s="3"/>
+      <c r="V127">
         <v>203</v>
       </c>
     </row>
-    <row r="128" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>601</v>
       </c>
@@ -14327,11 +16209,13 @@
       <c r="S128" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T128">
+      <c r="T128" s="3"/>
+      <c r="U128" s="3"/>
+      <c r="V128">
         <v>203</v>
       </c>
     </row>
-    <row r="129" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>603</v>
       </c>
@@ -14377,11 +16261,13 @@
       <c r="S129" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T129">
+      <c r="T129" s="3"/>
+      <c r="U129" s="3"/>
+      <c r="V129">
         <v>204</v>
       </c>
     </row>
-    <row r="130" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>609</v>
       </c>
@@ -14427,11 +16313,13 @@
       <c r="S130" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T130">
+      <c r="T130" s="3"/>
+      <c r="U130" s="3"/>
+      <c r="V130">
         <v>204</v>
       </c>
     </row>
-    <row r="131" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>615</v>
       </c>
@@ -14477,11 +16365,13 @@
       <c r="S131" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T131">
+      <c r="T131" s="3"/>
+      <c r="U131" s="3"/>
+      <c r="V131">
         <v>204</v>
       </c>
     </row>
-    <row r="132" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>621</v>
       </c>
@@ -14527,11 +16417,13 @@
       <c r="S132" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T132">
+      <c r="T132" s="3"/>
+      <c r="U132" s="3"/>
+      <c r="V132">
         <v>204</v>
       </c>
     </row>
-    <row r="133" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>627</v>
       </c>
@@ -14577,11 +16469,13 @@
       <c r="S133" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T133">
+      <c r="T133" s="3"/>
+      <c r="U133" s="3"/>
+      <c r="V133">
         <v>204</v>
       </c>
     </row>
-    <row r="134" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>633</v>
       </c>
@@ -14627,11 +16521,13 @@
       <c r="S134" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T134">
+      <c r="T134" s="3"/>
+      <c r="U134" s="3"/>
+      <c r="V134">
         <v>204</v>
       </c>
     </row>
-    <row r="135" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>639</v>
       </c>
@@ -14677,11 +16573,13 @@
       <c r="S135" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T135">
+      <c r="T135" s="3"/>
+      <c r="U135" s="3"/>
+      <c r="V135">
         <v>204</v>
       </c>
     </row>
-    <row r="136" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>641</v>
       </c>
@@ -14727,11 +16625,13 @@
       <c r="S136" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T136">
+      <c r="T136" s="3"/>
+      <c r="U136" s="3"/>
+      <c r="V136">
         <v>204</v>
       </c>
     </row>
-    <row r="137" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>647</v>
       </c>
@@ -14777,11 +16677,13 @@
       <c r="S137" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T137">
+      <c r="T137" s="3"/>
+      <c r="U137" s="3"/>
+      <c r="V137">
         <v>204</v>
       </c>
     </row>
-    <row r="138" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>653</v>
       </c>
@@ -14827,11 +16729,13 @@
       <c r="S138" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T138">
+      <c r="T138" s="3"/>
+      <c r="U138" s="3"/>
+      <c r="V138">
         <v>204</v>
       </c>
     </row>
-    <row r="139" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>658</v>
       </c>
@@ -14877,11 +16781,13 @@
       <c r="S139" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T139">
+      <c r="T139" s="3"/>
+      <c r="U139" s="3"/>
+      <c r="V139">
         <v>204</v>
       </c>
     </row>
-    <row r="140" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>663</v>
       </c>
@@ -14927,11 +16833,13 @@
       <c r="S140" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T140">
+      <c r="T140" s="3"/>
+      <c r="U140" s="3"/>
+      <c r="V140">
         <v>204</v>
       </c>
     </row>
-    <row r="141" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>668</v>
       </c>
@@ -14977,11 +16885,13 @@
       <c r="S141" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T141">
+      <c r="T141" s="3"/>
+      <c r="U141" s="3"/>
+      <c r="V141">
         <v>204</v>
       </c>
     </row>
-    <row r="142" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>673</v>
       </c>
@@ -15027,11 +16937,13 @@
       <c r="S142" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T142">
+      <c r="T142" s="3"/>
+      <c r="U142" s="3"/>
+      <c r="V142">
         <v>204</v>
       </c>
     </row>
-    <row r="143" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>679</v>
       </c>
@@ -15077,11 +16989,13 @@
       <c r="S143" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T143">
+      <c r="T143" s="3"/>
+      <c r="U143" s="3"/>
+      <c r="V143">
         <v>204</v>
       </c>
     </row>
-    <row r="144" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>684</v>
       </c>
@@ -15127,11 +17041,13 @@
       <c r="S144" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T144">
+      <c r="T144" s="3"/>
+      <c r="U144" s="3"/>
+      <c r="V144">
         <v>204</v>
       </c>
     </row>
-    <row r="145" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>690</v>
       </c>
@@ -15179,11 +17095,13 @@
       <c r="S145" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="T145">
+      <c r="T145" s="3"/>
+      <c r="U145" s="3"/>
+      <c r="V145">
         <v>204</v>
       </c>
     </row>
-    <row r="146" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>695</v>
       </c>
@@ -15231,11 +17149,13 @@
       <c r="S146" s="3" t="s">
         <v>991</v>
       </c>
-      <c r="T146">
+      <c r="T146" s="3"/>
+      <c r="U146" s="3"/>
+      <c r="V146">
         <v>205</v>
       </c>
     </row>
-    <row r="147" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>700</v>
       </c>
@@ -15283,11 +17203,13 @@
       <c r="S147" s="3" t="s">
         <v>991</v>
       </c>
-      <c r="T147">
+      <c r="T147" s="3"/>
+      <c r="U147" s="3"/>
+      <c r="V147">
         <v>205</v>
       </c>
     </row>
-    <row r="148" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>705</v>
       </c>
@@ -15335,11 +17257,13 @@
       <c r="S148" s="3" t="s">
         <v>991</v>
       </c>
-      <c r="T148">
+      <c r="T148" s="3"/>
+      <c r="U148" s="3"/>
+      <c r="V148">
         <v>205</v>
       </c>
     </row>
-    <row r="149" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>710</v>
       </c>
@@ -15387,11 +17311,13 @@
       <c r="S149" s="3" t="s">
         <v>991</v>
       </c>
-      <c r="T149">
+      <c r="T149" s="3"/>
+      <c r="U149" s="3"/>
+      <c r="V149">
         <v>205</v>
       </c>
     </row>
-    <row r="150" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>715</v>
       </c>
@@ -15439,11 +17365,13 @@
       <c r="S150" s="3" t="s">
         <v>991</v>
       </c>
-      <c r="T150">
+      <c r="T150" s="3"/>
+      <c r="U150" s="3"/>
+      <c r="V150">
         <v>205</v>
       </c>
     </row>
-    <row r="151" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>720</v>
       </c>
@@ -15491,11 +17419,13 @@
       <c r="S151" s="3" t="s">
         <v>991</v>
       </c>
-      <c r="T151">
+      <c r="T151" s="3"/>
+      <c r="U151" s="3"/>
+      <c r="V151">
         <v>205</v>
       </c>
     </row>
-    <row r="152" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>725</v>
       </c>
@@ -15543,11 +17473,13 @@
       <c r="S152" s="3" t="s">
         <v>991</v>
       </c>
-      <c r="T152">
+      <c r="T152" s="3"/>
+      <c r="U152" s="3"/>
+      <c r="V152">
         <v>205</v>
       </c>
     </row>
-    <row r="153" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>730</v>
       </c>
@@ -15595,11 +17527,13 @@
       <c r="S153" s="3" t="s">
         <v>991</v>
       </c>
-      <c r="T153">
+      <c r="T153" s="3"/>
+      <c r="U153" s="3"/>
+      <c r="V153">
         <v>205</v>
       </c>
     </row>
-    <row r="154" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>735</v>
       </c>
@@ -15647,11 +17581,13 @@
       <c r="S154" s="3" t="s">
         <v>991</v>
       </c>
-      <c r="T154">
+      <c r="T154" s="3"/>
+      <c r="U154" s="3"/>
+      <c r="V154">
         <v>205</v>
       </c>
     </row>
-    <row r="155" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>740</v>
       </c>
@@ -15699,11 +17635,13 @@
       <c r="S155" s="3" t="s">
         <v>991</v>
       </c>
-      <c r="T155">
+      <c r="T155" s="3"/>
+      <c r="U155" s="3"/>
+      <c r="V155">
         <v>205</v>
       </c>
     </row>
-    <row r="156" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>744</v>
       </c>
@@ -15751,11 +17689,13 @@
       <c r="S156" s="3" t="s">
         <v>991</v>
       </c>
-      <c r="T156">
+      <c r="T156" s="3"/>
+      <c r="U156" s="3"/>
+      <c r="V156">
         <v>205</v>
       </c>
     </row>
-    <row r="157" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>748</v>
       </c>
@@ -15803,11 +17743,13 @@
       <c r="S157" s="3" t="s">
         <v>991</v>
       </c>
-      <c r="T157">
+      <c r="T157" s="3"/>
+      <c r="U157" s="3"/>
+      <c r="V157">
         <v>205</v>
       </c>
     </row>
-    <row r="158" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>752</v>
       </c>
@@ -15855,11 +17797,13 @@
       <c r="S158" s="3" t="s">
         <v>991</v>
       </c>
-      <c r="T158">
+      <c r="T158" s="3"/>
+      <c r="U158" s="3"/>
+      <c r="V158">
         <v>205</v>
       </c>
     </row>
-    <row r="159" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>756</v>
       </c>
@@ -15907,11 +17851,13 @@
       <c r="S159" s="3" t="s">
         <v>991</v>
       </c>
-      <c r="T159">
+      <c r="T159" s="3"/>
+      <c r="U159" s="3"/>
+      <c r="V159">
         <v>205</v>
       </c>
     </row>
-    <row r="160" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>760</v>
       </c>
@@ -15959,11 +17905,13 @@
       <c r="S160" s="3" t="s">
         <v>991</v>
       </c>
-      <c r="T160">
+      <c r="T160" s="3"/>
+      <c r="U160" s="3"/>
+      <c r="V160">
         <v>205</v>
       </c>
     </row>
-    <row r="161" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>764</v>
       </c>
@@ -16011,11 +17959,13 @@
       <c r="S161" s="3" t="s">
         <v>991</v>
       </c>
-      <c r="T161">
+      <c r="T161" s="3"/>
+      <c r="U161" s="3"/>
+      <c r="V161">
         <v>205</v>
       </c>
     </row>
-    <row r="162" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>768</v>
       </c>
@@ -16063,11 +18013,13 @@
       <c r="S162" s="3" t="s">
         <v>991</v>
       </c>
-      <c r="T162">
+      <c r="T162" s="3"/>
+      <c r="U162" s="3"/>
+      <c r="V162">
         <v>205</v>
       </c>
     </row>
-    <row r="163" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>772</v>
       </c>
@@ -16115,11 +18067,13 @@
       <c r="S163" s="3" t="s">
         <v>991</v>
       </c>
-      <c r="T163">
+      <c r="T163" s="3"/>
+      <c r="U163" s="3"/>
+      <c r="V163">
         <v>205</v>
       </c>
     </row>
-    <row r="164" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>776</v>
       </c>
@@ -16167,11 +18121,13 @@
       <c r="S164" s="3" t="s">
         <v>991</v>
       </c>
-      <c r="T164">
+      <c r="T164" s="3"/>
+      <c r="U164" s="3"/>
+      <c r="V164">
         <v>205</v>
       </c>
     </row>
-    <row r="165" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>781</v>
       </c>
@@ -16217,11 +18173,13 @@
       <c r="S165" s="3" t="s">
         <v>991</v>
       </c>
-      <c r="T165">
+      <c r="T165" s="3"/>
+      <c r="U165" s="3"/>
+      <c r="V165">
         <v>205</v>
       </c>
     </row>
-    <row r="166" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>786</v>
       </c>
@@ -16267,8 +18225,5077 @@
       <c r="S166" s="3" t="s">
         <v>991</v>
       </c>
-      <c r="T166">
+      <c r="T166" s="3"/>
+      <c r="U166" s="3"/>
+      <c r="V166">
         <v>205</v>
+      </c>
+    </row>
+    <row r="167" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>999</v>
+      </c>
+      <c r="B167" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C167" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D167" t="s">
+        <v>1002</v>
+      </c>
+      <c r="E167" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F167" t="s">
+        <v>1004</v>
+      </c>
+      <c r="I167">
+        <v>8</v>
+      </c>
+      <c r="L167">
+        <v>485</v>
+      </c>
+      <c r="M167">
+        <v>215</v>
+      </c>
+      <c r="O167" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P167" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q167">
+        <v>1</v>
+      </c>
+      <c r="R167" s="3" t="s">
+        <v>1393</v>
+      </c>
+      <c r="S167" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T167" s="3" t="s">
+        <v>1400</v>
+      </c>
+      <c r="U167" s="3" t="s">
+        <v>1401</v>
+      </c>
+      <c r="V167">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="168" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B168" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C168" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D168" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E168" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F168" t="s">
+        <v>1004</v>
+      </c>
+      <c r="I168">
+        <v>8</v>
+      </c>
+      <c r="L168">
+        <v>590</v>
+      </c>
+      <c r="M168">
+        <v>215</v>
+      </c>
+      <c r="O168" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P168" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q168">
+        <v>1</v>
+      </c>
+      <c r="R168" s="3" t="s">
+        <v>1393</v>
+      </c>
+      <c r="S168" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T168" s="3" t="s">
+        <v>1400</v>
+      </c>
+      <c r="U168" s="3" t="s">
+        <v>1401</v>
+      </c>
+      <c r="V168">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="169" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B169" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C169" t="s">
+        <v>1011</v>
+      </c>
+      <c r="D169" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E169" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F169" t="s">
+        <v>1004</v>
+      </c>
+      <c r="I169">
+        <v>8</v>
+      </c>
+      <c r="L169">
+        <v>610</v>
+      </c>
+      <c r="M169">
+        <v>215</v>
+      </c>
+      <c r="O169" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P169" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q169">
+        <v>1</v>
+      </c>
+      <c r="R169" s="3" t="s">
+        <v>1393</v>
+      </c>
+      <c r="S169" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T169" s="3" t="s">
+        <v>1400</v>
+      </c>
+      <c r="U169" s="3" t="s">
+        <v>1401</v>
+      </c>
+      <c r="V169">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="170" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B170" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C170" t="s">
+        <v>1015</v>
+      </c>
+      <c r="D170" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E170" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F170" t="s">
+        <v>1004</v>
+      </c>
+      <c r="I170">
+        <v>8</v>
+      </c>
+      <c r="L170">
+        <v>750</v>
+      </c>
+      <c r="M170">
+        <v>215</v>
+      </c>
+      <c r="O170" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P170" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q170">
+        <v>1</v>
+      </c>
+      <c r="R170" s="3" t="s">
+        <v>1393</v>
+      </c>
+      <c r="S170" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T170" s="3" t="s">
+        <v>1400</v>
+      </c>
+      <c r="U170" s="3" t="s">
+        <v>1401</v>
+      </c>
+      <c r="V170">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="171" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B171" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C171" t="s">
+        <v>1019</v>
+      </c>
+      <c r="D171" t="s">
+        <v>1020</v>
+      </c>
+      <c r="E171" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F171" t="s">
+        <v>1004</v>
+      </c>
+      <c r="I171">
+        <v>8</v>
+      </c>
+      <c r="L171">
+        <v>810</v>
+      </c>
+      <c r="M171">
+        <v>215</v>
+      </c>
+      <c r="O171" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P171" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q171">
+        <v>1</v>
+      </c>
+      <c r="R171" s="3" t="s">
+        <v>1393</v>
+      </c>
+      <c r="S171" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T171" s="3" t="s">
+        <v>1400</v>
+      </c>
+      <c r="U171" s="3" t="s">
+        <v>1401</v>
+      </c>
+      <c r="V171">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="172" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B172" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C172" t="s">
+        <v>1023</v>
+      </c>
+      <c r="D172" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E172" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F172" t="s">
+        <v>1004</v>
+      </c>
+      <c r="I172">
+        <v>8</v>
+      </c>
+      <c r="L172">
+        <v>1010</v>
+      </c>
+      <c r="M172">
+        <v>215</v>
+      </c>
+      <c r="O172" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P172" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q172">
+        <v>1</v>
+      </c>
+      <c r="R172" s="3" t="s">
+        <v>1393</v>
+      </c>
+      <c r="S172" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T172" s="3" t="s">
+        <v>1400</v>
+      </c>
+      <c r="U172" s="3" t="s">
+        <v>1401</v>
+      </c>
+      <c r="V172">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="173" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B173" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C173" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D173" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E173" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F173" t="s">
+        <v>1004</v>
+      </c>
+      <c r="I173">
+        <v>8</v>
+      </c>
+      <c r="L173">
+        <v>1210</v>
+      </c>
+      <c r="M173">
+        <v>215</v>
+      </c>
+      <c r="O173" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P173" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q173">
+        <v>1</v>
+      </c>
+      <c r="R173" s="3" t="s">
+        <v>1393</v>
+      </c>
+      <c r="S173" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T173" s="3" t="s">
+        <v>1400</v>
+      </c>
+      <c r="U173" s="3" t="s">
+        <v>1401</v>
+      </c>
+      <c r="V173">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="174" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B174" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C174" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D174" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E174" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F174" t="s">
+        <v>1004</v>
+      </c>
+      <c r="I174">
+        <v>8</v>
+      </c>
+      <c r="L174">
+        <v>1410</v>
+      </c>
+      <c r="M174">
+        <v>215</v>
+      </c>
+      <c r="O174" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P174" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q174">
+        <v>1</v>
+      </c>
+      <c r="R174" s="3" t="s">
+        <v>1393</v>
+      </c>
+      <c r="S174" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T174" s="3" t="s">
+        <v>1400</v>
+      </c>
+      <c r="U174" s="3" t="s">
+        <v>1401</v>
+      </c>
+      <c r="V174">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="175" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B175" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C175" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D175" t="s">
+        <v>1036</v>
+      </c>
+      <c r="E175" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F175" t="s">
+        <v>1004</v>
+      </c>
+      <c r="I175">
+        <v>8</v>
+      </c>
+      <c r="L175">
+        <v>1610</v>
+      </c>
+      <c r="M175">
+        <v>215</v>
+      </c>
+      <c r="O175" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P175" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q175">
+        <v>1</v>
+      </c>
+      <c r="R175" s="3" t="s">
+        <v>1393</v>
+      </c>
+      <c r="S175" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T175" s="3" t="s">
+        <v>1400</v>
+      </c>
+      <c r="U175" s="3" t="s">
+        <v>1401</v>
+      </c>
+      <c r="V175">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="176" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B176" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C176" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D176" t="s">
+        <v>1040</v>
+      </c>
+      <c r="E176" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F176" t="s">
+        <v>1004</v>
+      </c>
+      <c r="I176">
+        <v>8</v>
+      </c>
+      <c r="L176">
+        <v>2010</v>
+      </c>
+      <c r="M176">
+        <v>215</v>
+      </c>
+      <c r="O176" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P176" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q176">
+        <v>1</v>
+      </c>
+      <c r="R176" s="3" t="s">
+        <v>1393</v>
+      </c>
+      <c r="S176" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T176" s="3" t="s">
+        <v>1400</v>
+      </c>
+      <c r="U176" s="3" t="s">
+        <v>1401</v>
+      </c>
+      <c r="V176">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="177" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B177" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C177" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D177" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E177" t="s">
+        <v>1045</v>
+      </c>
+      <c r="F177" t="s">
+        <v>1046</v>
+      </c>
+      <c r="I177">
+        <v>10</v>
+      </c>
+      <c r="L177">
+        <v>610</v>
+      </c>
+      <c r="M177">
+        <v>180</v>
+      </c>
+      <c r="O177" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P177" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q177">
+        <v>1</v>
+      </c>
+      <c r="R177" s="3" t="s">
+        <v>1393</v>
+      </c>
+      <c r="S177" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T177" s="3" t="s">
+        <v>1402</v>
+      </c>
+      <c r="U177" s="3" t="s">
+        <v>1403</v>
+      </c>
+      <c r="V177">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="178" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B178" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C178" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D178" t="s">
+        <v>1050</v>
+      </c>
+      <c r="E178" t="s">
+        <v>1045</v>
+      </c>
+      <c r="F178" t="s">
+        <v>1046</v>
+      </c>
+      <c r="I178">
+        <v>10</v>
+      </c>
+      <c r="L178">
+        <v>1410</v>
+      </c>
+      <c r="M178">
+        <v>180</v>
+      </c>
+      <c r="O178" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P178" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q178">
+        <v>1</v>
+      </c>
+      <c r="R178" s="3" t="s">
+        <v>1393</v>
+      </c>
+      <c r="S178" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T178" s="3" t="s">
+        <v>1402</v>
+      </c>
+      <c r="U178" s="3" t="s">
+        <v>1403</v>
+      </c>
+      <c r="V178">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="179" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B179" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C179" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D179" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E179" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F179" t="s">
+        <v>1056</v>
+      </c>
+      <c r="I179">
+        <v>12</v>
+      </c>
+      <c r="L179">
+        <v>510</v>
+      </c>
+      <c r="M179">
+        <v>160</v>
+      </c>
+      <c r="O179" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P179" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q179">
+        <v>1</v>
+      </c>
+      <c r="R179" s="3" t="s">
+        <v>1393</v>
+      </c>
+      <c r="S179" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T179" s="3" t="s">
+        <v>1404</v>
+      </c>
+      <c r="U179" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="V179">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="180" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B180" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C180" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D180" t="s">
+        <v>1060</v>
+      </c>
+      <c r="E180" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F180" t="s">
+        <v>1056</v>
+      </c>
+      <c r="I180">
+        <v>12</v>
+      </c>
+      <c r="L180">
+        <v>610</v>
+      </c>
+      <c r="M180">
+        <v>160</v>
+      </c>
+      <c r="O180" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P180" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q180">
+        <v>1</v>
+      </c>
+      <c r="R180" s="3" t="s">
+        <v>1393</v>
+      </c>
+      <c r="S180" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T180" s="3" t="s">
+        <v>1404</v>
+      </c>
+      <c r="U180" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="V180">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="181" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B181" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C181" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D181" t="s">
+        <v>1064</v>
+      </c>
+      <c r="E181" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F181" t="s">
+        <v>1056</v>
+      </c>
+      <c r="I181">
+        <v>12</v>
+      </c>
+      <c r="L181">
+        <v>810</v>
+      </c>
+      <c r="M181">
+        <v>160</v>
+      </c>
+      <c r="O181" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P181" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q181">
+        <v>1</v>
+      </c>
+      <c r="R181" s="3" t="s">
+        <v>1393</v>
+      </c>
+      <c r="S181" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T181" s="3" t="s">
+        <v>1404</v>
+      </c>
+      <c r="U181" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="V181">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="182" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B182" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C182" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D182" t="s">
+        <v>1068</v>
+      </c>
+      <c r="E182" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F182" t="s">
+        <v>1056</v>
+      </c>
+      <c r="I182">
+        <v>12</v>
+      </c>
+      <c r="L182">
+        <v>1010</v>
+      </c>
+      <c r="M182">
+        <v>160</v>
+      </c>
+      <c r="O182" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P182" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q182">
+        <v>1</v>
+      </c>
+      <c r="R182" s="3" t="s">
+        <v>1393</v>
+      </c>
+      <c r="S182" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T182" s="3" t="s">
+        <v>1404</v>
+      </c>
+      <c r="U182" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="V182">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="183" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B183" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C183" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D183" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E183" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F183" t="s">
+        <v>1056</v>
+      </c>
+      <c r="I183">
+        <v>12</v>
+      </c>
+      <c r="L183">
+        <v>1210</v>
+      </c>
+      <c r="M183">
+        <v>160</v>
+      </c>
+      <c r="O183" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P183" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q183">
+        <v>1</v>
+      </c>
+      <c r="R183" s="3" t="s">
+        <v>1393</v>
+      </c>
+      <c r="S183" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T183" s="3" t="s">
+        <v>1404</v>
+      </c>
+      <c r="U183" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="V183">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="184" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B184" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C184" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D184" t="s">
+        <v>1076</v>
+      </c>
+      <c r="E184" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F184" t="s">
+        <v>1056</v>
+      </c>
+      <c r="I184">
+        <v>12</v>
+      </c>
+      <c r="L184">
+        <v>1410</v>
+      </c>
+      <c r="M184">
+        <v>160</v>
+      </c>
+      <c r="O184" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P184" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q184">
+        <v>1</v>
+      </c>
+      <c r="R184" s="3" t="s">
+        <v>1393</v>
+      </c>
+      <c r="S184" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T184" s="3" t="s">
+        <v>1404</v>
+      </c>
+      <c r="U184" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="V184">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="185" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B185" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C185" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D185" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E185" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F185" t="s">
+        <v>1056</v>
+      </c>
+      <c r="I185">
+        <v>12</v>
+      </c>
+      <c r="L185">
+        <v>1510</v>
+      </c>
+      <c r="M185">
+        <v>160</v>
+      </c>
+      <c r="O185" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P185" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q185">
+        <v>1</v>
+      </c>
+      <c r="R185" s="3" t="s">
+        <v>1393</v>
+      </c>
+      <c r="S185" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T185" s="3" t="s">
+        <v>1404</v>
+      </c>
+      <c r="U185" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="V185">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="186" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B186" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C186" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D186" t="s">
+        <v>1084</v>
+      </c>
+      <c r="E186" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F186" t="s">
+        <v>1056</v>
+      </c>
+      <c r="I186">
+        <v>12</v>
+      </c>
+      <c r="L186">
+        <v>1610</v>
+      </c>
+      <c r="M186">
+        <v>160</v>
+      </c>
+      <c r="O186" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P186" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q186">
+        <v>1</v>
+      </c>
+      <c r="R186" s="3" t="s">
+        <v>1393</v>
+      </c>
+      <c r="S186" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T186" s="3" t="s">
+        <v>1404</v>
+      </c>
+      <c r="U186" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="V186">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="187" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B187" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C187" t="s">
+        <v>1087</v>
+      </c>
+      <c r="D187" t="s">
+        <v>1088</v>
+      </c>
+      <c r="E187" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F187" t="s">
+        <v>1056</v>
+      </c>
+      <c r="I187">
+        <v>12</v>
+      </c>
+      <c r="L187">
+        <v>1810</v>
+      </c>
+      <c r="M187">
+        <v>160</v>
+      </c>
+      <c r="O187" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P187" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q187">
+        <v>1</v>
+      </c>
+      <c r="R187" s="3" t="s">
+        <v>1393</v>
+      </c>
+      <c r="S187" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T187" s="3" t="s">
+        <v>1404</v>
+      </c>
+      <c r="U187" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="V187">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="188" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B188" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C188" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D188" t="s">
+        <v>1092</v>
+      </c>
+      <c r="E188" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F188" t="s">
+        <v>1056</v>
+      </c>
+      <c r="I188">
+        <v>12</v>
+      </c>
+      <c r="L188">
+        <v>2010</v>
+      </c>
+      <c r="M188">
+        <v>160</v>
+      </c>
+      <c r="O188" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P188" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q188">
+        <v>1</v>
+      </c>
+      <c r="R188" s="3" t="s">
+        <v>1393</v>
+      </c>
+      <c r="S188" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T188" s="3" t="s">
+        <v>1404</v>
+      </c>
+      <c r="U188" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="V188">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="189" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B189" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C189" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D189" t="s">
+        <v>1095</v>
+      </c>
+      <c r="E189" t="s">
+        <v>1096</v>
+      </c>
+      <c r="F189" t="s">
+        <v>1056</v>
+      </c>
+      <c r="I189">
+        <v>12</v>
+      </c>
+      <c r="L189">
+        <v>610</v>
+      </c>
+      <c r="M189">
+        <v>160</v>
+      </c>
+      <c r="O189" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P189" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q189">
+        <v>1</v>
+      </c>
+      <c r="R189" s="3" t="s">
+        <v>1393</v>
+      </c>
+      <c r="S189" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T189" s="3" t="s">
+        <v>1397</v>
+      </c>
+      <c r="U189" s="3" t="s">
+        <v>1406</v>
+      </c>
+      <c r="V189">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="190" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B190" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C190" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D190" t="s">
+        <v>1099</v>
+      </c>
+      <c r="E190" t="s">
+        <v>1096</v>
+      </c>
+      <c r="F190" t="s">
+        <v>1056</v>
+      </c>
+      <c r="I190">
+        <v>12</v>
+      </c>
+      <c r="L190">
+        <v>810</v>
+      </c>
+      <c r="M190">
+        <v>160</v>
+      </c>
+      <c r="O190" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P190" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q190">
+        <v>1</v>
+      </c>
+      <c r="R190" s="3" t="s">
+        <v>1393</v>
+      </c>
+      <c r="S190" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T190" s="3" t="s">
+        <v>1397</v>
+      </c>
+      <c r="U190" s="3" t="s">
+        <v>1406</v>
+      </c>
+      <c r="V190">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="191" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B191" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C191" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D191" t="s">
+        <v>1102</v>
+      </c>
+      <c r="E191" t="s">
+        <v>1096</v>
+      </c>
+      <c r="F191" t="s">
+        <v>1056</v>
+      </c>
+      <c r="I191">
+        <v>12</v>
+      </c>
+      <c r="L191">
+        <v>1010</v>
+      </c>
+      <c r="M191">
+        <v>160</v>
+      </c>
+      <c r="O191" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P191" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q191">
+        <v>1</v>
+      </c>
+      <c r="R191" s="3" t="s">
+        <v>1393</v>
+      </c>
+      <c r="S191" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T191" s="3" t="s">
+        <v>1397</v>
+      </c>
+      <c r="U191" s="3" t="s">
+        <v>1406</v>
+      </c>
+      <c r="V191">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="192" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B192" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C192" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D192" t="s">
+        <v>1105</v>
+      </c>
+      <c r="E192" t="s">
+        <v>1096</v>
+      </c>
+      <c r="F192" t="s">
+        <v>1056</v>
+      </c>
+      <c r="I192">
+        <v>12</v>
+      </c>
+      <c r="L192">
+        <v>1210</v>
+      </c>
+      <c r="M192">
+        <v>160</v>
+      </c>
+      <c r="O192" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P192" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q192">
+        <v>1</v>
+      </c>
+      <c r="R192" s="3" t="s">
+        <v>1393</v>
+      </c>
+      <c r="S192" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T192" s="3" t="s">
+        <v>1397</v>
+      </c>
+      <c r="U192" s="3" t="s">
+        <v>1406</v>
+      </c>
+      <c r="V192">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="193" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B193" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C193" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D193" t="s">
+        <v>1108</v>
+      </c>
+      <c r="E193" t="s">
+        <v>1096</v>
+      </c>
+      <c r="F193" t="s">
+        <v>1056</v>
+      </c>
+      <c r="I193">
+        <v>12</v>
+      </c>
+      <c r="L193">
+        <v>1610</v>
+      </c>
+      <c r="M193">
+        <v>160</v>
+      </c>
+      <c r="O193" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P193" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q193">
+        <v>1</v>
+      </c>
+      <c r="R193" s="3" t="s">
+        <v>1393</v>
+      </c>
+      <c r="S193" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T193" s="3" t="s">
+        <v>1397</v>
+      </c>
+      <c r="U193" s="3" t="s">
+        <v>1406</v>
+      </c>
+      <c r="V193">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="194" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B194" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C194" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D194" t="s">
+        <v>1112</v>
+      </c>
+      <c r="E194" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F194" t="s">
+        <v>1114</v>
+      </c>
+      <c r="I194">
+        <v>16</v>
+      </c>
+      <c r="L194">
+        <v>610</v>
+      </c>
+      <c r="M194">
+        <v>130</v>
+      </c>
+      <c r="O194" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P194" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q194">
+        <v>1</v>
+      </c>
+      <c r="R194" s="3" t="s">
+        <v>1393</v>
+      </c>
+      <c r="S194" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T194" s="3" t="s">
+        <v>1398</v>
+      </c>
+      <c r="U194" s="3" t="s">
+        <v>1407</v>
+      </c>
+      <c r="V194">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="195" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B195" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C195" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D195" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E195" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F195" t="s">
+        <v>1114</v>
+      </c>
+      <c r="I195">
+        <v>16</v>
+      </c>
+      <c r="L195">
+        <v>810</v>
+      </c>
+      <c r="M195">
+        <v>130</v>
+      </c>
+      <c r="O195" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P195" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q195">
+        <v>1</v>
+      </c>
+      <c r="R195" s="3" t="s">
+        <v>1393</v>
+      </c>
+      <c r="S195" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T195" s="3" t="s">
+        <v>1398</v>
+      </c>
+      <c r="U195" s="3" t="s">
+        <v>1407</v>
+      </c>
+      <c r="V195">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="196" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B196" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C196" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D196" t="s">
+        <v>1122</v>
+      </c>
+      <c r="E196" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F196" t="s">
+        <v>1114</v>
+      </c>
+      <c r="I196">
+        <v>16</v>
+      </c>
+      <c r="L196">
+        <v>1010</v>
+      </c>
+      <c r="M196">
+        <v>130</v>
+      </c>
+      <c r="O196" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P196" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q196">
+        <v>1</v>
+      </c>
+      <c r="R196" s="3" t="s">
+        <v>1393</v>
+      </c>
+      <c r="S196" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T196" s="3" t="s">
+        <v>1398</v>
+      </c>
+      <c r="U196" s="3" t="s">
+        <v>1407</v>
+      </c>
+      <c r="V196">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="197" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B197" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C197" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D197" t="s">
+        <v>1126</v>
+      </c>
+      <c r="E197" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F197" t="s">
+        <v>1114</v>
+      </c>
+      <c r="I197">
+        <v>16</v>
+      </c>
+      <c r="L197">
+        <v>1210</v>
+      </c>
+      <c r="M197">
+        <v>130</v>
+      </c>
+      <c r="O197" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P197" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q197">
+        <v>1</v>
+      </c>
+      <c r="R197" s="3" t="s">
+        <v>1393</v>
+      </c>
+      <c r="S197" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T197" s="3" t="s">
+        <v>1398</v>
+      </c>
+      <c r="U197" s="3" t="s">
+        <v>1407</v>
+      </c>
+      <c r="V197">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="198" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B198" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C198" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D198" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E198" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F198" t="s">
+        <v>1114</v>
+      </c>
+      <c r="I198">
+        <v>16</v>
+      </c>
+      <c r="L198">
+        <v>1410</v>
+      </c>
+      <c r="M198">
+        <v>130</v>
+      </c>
+      <c r="O198" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P198" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q198">
+        <v>1</v>
+      </c>
+      <c r="R198" s="3" t="s">
+        <v>1393</v>
+      </c>
+      <c r="S198" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T198" s="3" t="s">
+        <v>1398</v>
+      </c>
+      <c r="U198" s="3" t="s">
+        <v>1407</v>
+      </c>
+      <c r="V198">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="199" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B199" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C199" t="s">
+        <v>1133</v>
+      </c>
+      <c r="D199" t="s">
+        <v>1134</v>
+      </c>
+      <c r="E199" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F199" t="s">
+        <v>1114</v>
+      </c>
+      <c r="I199">
+        <v>16</v>
+      </c>
+      <c r="L199">
+        <v>1510</v>
+      </c>
+      <c r="M199">
+        <v>130</v>
+      </c>
+      <c r="O199" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P199" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q199">
+        <v>1</v>
+      </c>
+      <c r="R199" s="3" t="s">
+        <v>1393</v>
+      </c>
+      <c r="S199" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T199" s="3" t="s">
+        <v>1398</v>
+      </c>
+      <c r="U199" s="3" t="s">
+        <v>1407</v>
+      </c>
+      <c r="V199">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="200" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B200" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C200" t="s">
+        <v>1137</v>
+      </c>
+      <c r="D200" t="s">
+        <v>1138</v>
+      </c>
+      <c r="E200" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F200" t="s">
+        <v>1114</v>
+      </c>
+      <c r="I200">
+        <v>16</v>
+      </c>
+      <c r="L200">
+        <v>1610</v>
+      </c>
+      <c r="M200">
+        <v>130</v>
+      </c>
+      <c r="O200" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P200" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q200">
+        <v>1</v>
+      </c>
+      <c r="R200" s="3" t="s">
+        <v>1393</v>
+      </c>
+      <c r="S200" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T200" s="3" t="s">
+        <v>1398</v>
+      </c>
+      <c r="U200" s="3" t="s">
+        <v>1407</v>
+      </c>
+      <c r="V200">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="201" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B201" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C201" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D201" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E201" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F201" t="s">
+        <v>1114</v>
+      </c>
+      <c r="I201">
+        <v>16</v>
+      </c>
+      <c r="L201">
+        <v>2010</v>
+      </c>
+      <c r="M201">
+        <v>130</v>
+      </c>
+      <c r="O201" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P201" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q201">
+        <v>1</v>
+      </c>
+      <c r="R201" s="3" t="s">
+        <v>1393</v>
+      </c>
+      <c r="S201" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T201" s="3" t="s">
+        <v>1398</v>
+      </c>
+      <c r="U201" s="3" t="s">
+        <v>1407</v>
+      </c>
+      <c r="V201">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="202" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B202" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C202" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D202" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E202" t="s">
+        <v>1147</v>
+      </c>
+      <c r="F202" t="s">
+        <v>1148</v>
+      </c>
+      <c r="I202">
+        <v>8</v>
+      </c>
+      <c r="L202">
+        <v>410</v>
+      </c>
+      <c r="M202">
+        <v>350</v>
+      </c>
+      <c r="O202" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P202" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q202">
+        <v>2</v>
+      </c>
+      <c r="R202" s="3" t="s">
+        <v>1393</v>
+      </c>
+      <c r="S202" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T202" s="3" t="s">
+        <v>1400</v>
+      </c>
+      <c r="U202" s="3" t="s">
+        <v>1401</v>
+      </c>
+      <c r="V202">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="203" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B203" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C203" t="s">
+        <v>1151</v>
+      </c>
+      <c r="D203" t="s">
+        <v>1152</v>
+      </c>
+      <c r="E203" t="s">
+        <v>1147</v>
+      </c>
+      <c r="F203" t="s">
+        <v>1148</v>
+      </c>
+      <c r="I203">
+        <v>8</v>
+      </c>
+      <c r="L203">
+        <v>610</v>
+      </c>
+      <c r="M203">
+        <v>350</v>
+      </c>
+      <c r="O203" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P203" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q203">
+        <v>2</v>
+      </c>
+      <c r="R203" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S203" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T203" s="3" t="s">
+        <v>1400</v>
+      </c>
+      <c r="U203" s="3" t="s">
+        <v>1401</v>
+      </c>
+      <c r="V203">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="204" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B204" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C204" t="s">
+        <v>1155</v>
+      </c>
+      <c r="D204" t="s">
+        <v>1156</v>
+      </c>
+      <c r="E204" t="s">
+        <v>1147</v>
+      </c>
+      <c r="F204" t="s">
+        <v>1148</v>
+      </c>
+      <c r="I204">
+        <v>8</v>
+      </c>
+      <c r="L204">
+        <v>810</v>
+      </c>
+      <c r="M204">
+        <v>350</v>
+      </c>
+      <c r="O204" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P204" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q204">
+        <v>2</v>
+      </c>
+      <c r="R204" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S204" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T204" s="3" t="s">
+        <v>1400</v>
+      </c>
+      <c r="U204" s="3" t="s">
+        <v>1401</v>
+      </c>
+      <c r="V204">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="205" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B205" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C205" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D205" t="s">
+        <v>1160</v>
+      </c>
+      <c r="E205" t="s">
+        <v>1147</v>
+      </c>
+      <c r="F205" t="s">
+        <v>1148</v>
+      </c>
+      <c r="I205">
+        <v>8</v>
+      </c>
+      <c r="L205">
+        <v>1010</v>
+      </c>
+      <c r="M205">
+        <v>350</v>
+      </c>
+      <c r="O205" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P205" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q205">
+        <v>2</v>
+      </c>
+      <c r="R205" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S205" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T205" s="3" t="s">
+        <v>1400</v>
+      </c>
+      <c r="U205" s="3" t="s">
+        <v>1401</v>
+      </c>
+      <c r="V205">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="206" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B206" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C206" t="s">
+        <v>1163</v>
+      </c>
+      <c r="D206" t="s">
+        <v>1164</v>
+      </c>
+      <c r="E206" t="s">
+        <v>1147</v>
+      </c>
+      <c r="F206" t="s">
+        <v>1148</v>
+      </c>
+      <c r="I206">
+        <v>8</v>
+      </c>
+      <c r="L206">
+        <v>1210</v>
+      </c>
+      <c r="M206">
+        <v>350</v>
+      </c>
+      <c r="O206" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P206" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q206">
+        <v>2</v>
+      </c>
+      <c r="R206" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S206" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T206" s="3" t="s">
+        <v>1400</v>
+      </c>
+      <c r="U206" s="3" t="s">
+        <v>1401</v>
+      </c>
+      <c r="V206">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="207" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B207" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C207" t="s">
+        <v>1167</v>
+      </c>
+      <c r="D207" t="s">
+        <v>1168</v>
+      </c>
+      <c r="E207" t="s">
+        <v>1147</v>
+      </c>
+      <c r="F207" t="s">
+        <v>1148</v>
+      </c>
+      <c r="I207">
+        <v>8</v>
+      </c>
+      <c r="L207">
+        <v>1510</v>
+      </c>
+      <c r="M207">
+        <v>350</v>
+      </c>
+      <c r="O207" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P207" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q207">
+        <v>2</v>
+      </c>
+      <c r="R207" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S207" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T207" s="3" t="s">
+        <v>1400</v>
+      </c>
+      <c r="U207" s="3" t="s">
+        <v>1401</v>
+      </c>
+      <c r="V207">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="208" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B208" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C208" t="s">
+        <v>1171</v>
+      </c>
+      <c r="D208" t="s">
+        <v>1172</v>
+      </c>
+      <c r="E208" t="s">
+        <v>1147</v>
+      </c>
+      <c r="F208" t="s">
+        <v>1148</v>
+      </c>
+      <c r="I208">
+        <v>8</v>
+      </c>
+      <c r="L208">
+        <v>1610</v>
+      </c>
+      <c r="M208">
+        <v>350</v>
+      </c>
+      <c r="O208" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P208" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q208">
+        <v>2</v>
+      </c>
+      <c r="R208" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S208" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T208" s="3" t="s">
+        <v>1400</v>
+      </c>
+      <c r="U208" s="3" t="s">
+        <v>1401</v>
+      </c>
+      <c r="V208">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="209" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B209" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C209" t="s">
+        <v>1175</v>
+      </c>
+      <c r="D209" t="s">
+        <v>1176</v>
+      </c>
+      <c r="E209" t="s">
+        <v>1147</v>
+      </c>
+      <c r="F209" t="s">
+        <v>1148</v>
+      </c>
+      <c r="I209">
+        <v>8</v>
+      </c>
+      <c r="L209">
+        <v>2010</v>
+      </c>
+      <c r="M209">
+        <v>350</v>
+      </c>
+      <c r="O209" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P209" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q209">
+        <v>2</v>
+      </c>
+      <c r="R209" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S209" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T209" s="3" t="s">
+        <v>1400</v>
+      </c>
+      <c r="U209" s="3" t="s">
+        <v>1401</v>
+      </c>
+      <c r="V209">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="210" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B210" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C210" t="s">
+        <v>1179</v>
+      </c>
+      <c r="D210" t="s">
+        <v>1180</v>
+      </c>
+      <c r="E210" t="s">
+        <v>1181</v>
+      </c>
+      <c r="F210" t="s">
+        <v>1182</v>
+      </c>
+      <c r="I210">
+        <v>10</v>
+      </c>
+      <c r="L210">
+        <v>410</v>
+      </c>
+      <c r="M210">
+        <v>330</v>
+      </c>
+      <c r="O210" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P210" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q210">
+        <v>2</v>
+      </c>
+      <c r="R210" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S210" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T210" s="3" t="s">
+        <v>1402</v>
+      </c>
+      <c r="U210" s="3" t="s">
+        <v>1403</v>
+      </c>
+      <c r="V210">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="211" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B211" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C211" t="s">
+        <v>1185</v>
+      </c>
+      <c r="D211" t="s">
+        <v>1186</v>
+      </c>
+      <c r="E211" t="s">
+        <v>1181</v>
+      </c>
+      <c r="F211" t="s">
+        <v>1182</v>
+      </c>
+      <c r="I211">
+        <v>10</v>
+      </c>
+      <c r="L211">
+        <v>610</v>
+      </c>
+      <c r="M211">
+        <v>330</v>
+      </c>
+      <c r="O211" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P211" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q211">
+        <v>2</v>
+      </c>
+      <c r="R211" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S211" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T211" s="3" t="s">
+        <v>1402</v>
+      </c>
+      <c r="U211" s="3" t="s">
+        <v>1403</v>
+      </c>
+      <c r="V211">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="212" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B212" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C212" t="s">
+        <v>1189</v>
+      </c>
+      <c r="D212" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E212" t="s">
+        <v>1181</v>
+      </c>
+      <c r="F212" t="s">
+        <v>1182</v>
+      </c>
+      <c r="I212">
+        <v>10</v>
+      </c>
+      <c r="L212">
+        <v>810</v>
+      </c>
+      <c r="M212">
+        <v>330</v>
+      </c>
+      <c r="O212" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P212" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q212">
+        <v>2</v>
+      </c>
+      <c r="R212" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S212" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T212" s="3" t="s">
+        <v>1402</v>
+      </c>
+      <c r="U212" s="3" t="s">
+        <v>1403</v>
+      </c>
+      <c r="V212">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="213" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B213" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C213" t="s">
+        <v>1193</v>
+      </c>
+      <c r="D213" t="s">
+        <v>1194</v>
+      </c>
+      <c r="E213" t="s">
+        <v>1181</v>
+      </c>
+      <c r="F213" t="s">
+        <v>1182</v>
+      </c>
+      <c r="I213">
+        <v>10</v>
+      </c>
+      <c r="L213">
+        <v>1010</v>
+      </c>
+      <c r="M213">
+        <v>330</v>
+      </c>
+      <c r="O213" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P213" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q213">
+        <v>2</v>
+      </c>
+      <c r="R213" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S213" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T213" s="3" t="s">
+        <v>1402</v>
+      </c>
+      <c r="U213" s="3" t="s">
+        <v>1403</v>
+      </c>
+      <c r="V213">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="214" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B214" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C214" t="s">
+        <v>1197</v>
+      </c>
+      <c r="D214" t="s">
+        <v>1198</v>
+      </c>
+      <c r="E214" t="s">
+        <v>1181</v>
+      </c>
+      <c r="F214" t="s">
+        <v>1182</v>
+      </c>
+      <c r="I214">
+        <v>10</v>
+      </c>
+      <c r="L214">
+        <v>1210</v>
+      </c>
+      <c r="M214">
+        <v>330</v>
+      </c>
+      <c r="O214" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P214" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q214">
+        <v>2</v>
+      </c>
+      <c r="R214" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S214" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T214" s="3" t="s">
+        <v>1402</v>
+      </c>
+      <c r="U214" s="3" t="s">
+        <v>1403</v>
+      </c>
+      <c r="V214">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="215" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B215" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C215" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D215" t="s">
+        <v>1202</v>
+      </c>
+      <c r="E215" t="s">
+        <v>1181</v>
+      </c>
+      <c r="F215" t="s">
+        <v>1182</v>
+      </c>
+      <c r="I215">
+        <v>10</v>
+      </c>
+      <c r="L215">
+        <v>1410</v>
+      </c>
+      <c r="M215">
+        <v>330</v>
+      </c>
+      <c r="O215" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P215" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q215">
+        <v>2</v>
+      </c>
+      <c r="R215" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S215" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T215" s="3" t="s">
+        <v>1402</v>
+      </c>
+      <c r="U215" s="3" t="s">
+        <v>1403</v>
+      </c>
+      <c r="V215">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="216" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B216" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C216" t="s">
+        <v>1205</v>
+      </c>
+      <c r="D216" t="s">
+        <v>1206</v>
+      </c>
+      <c r="E216" t="s">
+        <v>1181</v>
+      </c>
+      <c r="F216" t="s">
+        <v>1182</v>
+      </c>
+      <c r="I216">
+        <v>10</v>
+      </c>
+      <c r="L216">
+        <v>1510</v>
+      </c>
+      <c r="M216">
+        <v>330</v>
+      </c>
+      <c r="O216" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P216" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q216">
+        <v>2</v>
+      </c>
+      <c r="R216" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S216" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T216" s="3" t="s">
+        <v>1402</v>
+      </c>
+      <c r="U216" s="3" t="s">
+        <v>1403</v>
+      </c>
+      <c r="V216">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="217" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B217" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C217" t="s">
+        <v>1209</v>
+      </c>
+      <c r="D217" t="s">
+        <v>1210</v>
+      </c>
+      <c r="E217" t="s">
+        <v>1181</v>
+      </c>
+      <c r="F217" t="s">
+        <v>1182</v>
+      </c>
+      <c r="I217">
+        <v>10</v>
+      </c>
+      <c r="L217">
+        <v>1610</v>
+      </c>
+      <c r="M217">
+        <v>330</v>
+      </c>
+      <c r="O217" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P217" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q217">
+        <v>2</v>
+      </c>
+      <c r="R217" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S217" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T217" s="3" t="s">
+        <v>1402</v>
+      </c>
+      <c r="U217" s="3" t="s">
+        <v>1403</v>
+      </c>
+      <c r="V217">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="218" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B218" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C218" t="s">
+        <v>1213</v>
+      </c>
+      <c r="D218" t="s">
+        <v>1214</v>
+      </c>
+      <c r="E218" t="s">
+        <v>1181</v>
+      </c>
+      <c r="F218" t="s">
+        <v>1182</v>
+      </c>
+      <c r="I218">
+        <v>10</v>
+      </c>
+      <c r="L218">
+        <v>1810</v>
+      </c>
+      <c r="M218">
+        <v>330</v>
+      </c>
+      <c r="O218" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P218" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q218">
+        <v>2</v>
+      </c>
+      <c r="R218" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S218" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T218" s="3" t="s">
+        <v>1402</v>
+      </c>
+      <c r="U218" s="3" t="s">
+        <v>1403</v>
+      </c>
+      <c r="V218">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="219" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>1215</v>
+      </c>
+      <c r="B219" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C219" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D219" t="s">
+        <v>1218</v>
+      </c>
+      <c r="E219" t="s">
+        <v>1181</v>
+      </c>
+      <c r="F219" t="s">
+        <v>1182</v>
+      </c>
+      <c r="I219">
+        <v>10</v>
+      </c>
+      <c r="L219">
+        <v>2010</v>
+      </c>
+      <c r="M219">
+        <v>330</v>
+      </c>
+      <c r="O219" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P219" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q219">
+        <v>2</v>
+      </c>
+      <c r="R219" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S219" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T219" s="3" t="s">
+        <v>1402</v>
+      </c>
+      <c r="U219" s="3" t="s">
+        <v>1403</v>
+      </c>
+      <c r="V219">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="220" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B220" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C220" t="s">
+        <v>1221</v>
+      </c>
+      <c r="D220" t="s">
+        <v>1222</v>
+      </c>
+      <c r="E220" t="s">
+        <v>1223</v>
+      </c>
+      <c r="F220" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I220">
+        <v>12</v>
+      </c>
+      <c r="L220">
+        <v>210</v>
+      </c>
+      <c r="M220">
+        <v>275</v>
+      </c>
+      <c r="O220" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P220" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q220">
+        <v>2</v>
+      </c>
+      <c r="R220" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S220" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T220" s="3" t="s">
+        <v>1404</v>
+      </c>
+      <c r="U220" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="V220">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="221" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B221" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C221" t="s">
+        <v>1227</v>
+      </c>
+      <c r="D221" t="s">
+        <v>1228</v>
+      </c>
+      <c r="E221" t="s">
+        <v>1223</v>
+      </c>
+      <c r="F221" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I221">
+        <v>12</v>
+      </c>
+      <c r="L221">
+        <v>410</v>
+      </c>
+      <c r="M221">
+        <v>275</v>
+      </c>
+      <c r="O221" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P221" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q221">
+        <v>2</v>
+      </c>
+      <c r="R221" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S221" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T221" s="3" t="s">
+        <v>1404</v>
+      </c>
+      <c r="U221" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="V221">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="222" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B222" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C222" t="s">
+        <v>1231</v>
+      </c>
+      <c r="D222" t="s">
+        <v>1232</v>
+      </c>
+      <c r="E222" t="s">
+        <v>1223</v>
+      </c>
+      <c r="F222" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I222">
+        <v>12</v>
+      </c>
+      <c r="L222">
+        <v>610</v>
+      </c>
+      <c r="M222">
+        <v>275</v>
+      </c>
+      <c r="O222" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P222" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q222">
+        <v>2</v>
+      </c>
+      <c r="R222" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S222" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T222" s="3" t="s">
+        <v>1404</v>
+      </c>
+      <c r="U222" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="V222">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="223" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B223" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C223" t="s">
+        <v>1235</v>
+      </c>
+      <c r="D223" t="s">
+        <v>1236</v>
+      </c>
+      <c r="E223" t="s">
+        <v>1223</v>
+      </c>
+      <c r="F223" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I223">
+        <v>12</v>
+      </c>
+      <c r="L223">
+        <v>810</v>
+      </c>
+      <c r="M223">
+        <v>275</v>
+      </c>
+      <c r="O223" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P223" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q223">
+        <v>2</v>
+      </c>
+      <c r="R223" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S223" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T223" s="3" t="s">
+        <v>1404</v>
+      </c>
+      <c r="U223" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="V223">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="224" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B224" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C224" t="s">
+        <v>1239</v>
+      </c>
+      <c r="D224" t="s">
+        <v>1240</v>
+      </c>
+      <c r="E224" t="s">
+        <v>1223</v>
+      </c>
+      <c r="F224" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I224">
+        <v>12</v>
+      </c>
+      <c r="L224">
+        <v>1010</v>
+      </c>
+      <c r="M224">
+        <v>275</v>
+      </c>
+      <c r="O224" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P224" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q224">
+        <v>2</v>
+      </c>
+      <c r="R224" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S224" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T224" s="3" t="s">
+        <v>1404</v>
+      </c>
+      <c r="U224" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="V224">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="225" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B225" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C225" t="s">
+        <v>1243</v>
+      </c>
+      <c r="D225" t="s">
+        <v>1244</v>
+      </c>
+      <c r="E225" t="s">
+        <v>1223</v>
+      </c>
+      <c r="F225" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I225">
+        <v>12</v>
+      </c>
+      <c r="L225">
+        <v>1110</v>
+      </c>
+      <c r="M225">
+        <v>275</v>
+      </c>
+      <c r="O225" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P225" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q225">
+        <v>2</v>
+      </c>
+      <c r="R225" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S225" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T225" s="3" t="s">
+        <v>1404</v>
+      </c>
+      <c r="U225" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="V225">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="226" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B226" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C226" t="s">
+        <v>1247</v>
+      </c>
+      <c r="D226" t="s">
+        <v>1248</v>
+      </c>
+      <c r="E226" t="s">
+        <v>1223</v>
+      </c>
+      <c r="F226" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I226">
+        <v>12</v>
+      </c>
+      <c r="L226">
+        <v>1210</v>
+      </c>
+      <c r="M226">
+        <v>275</v>
+      </c>
+      <c r="O226" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P226" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q226">
+        <v>2</v>
+      </c>
+      <c r="R226" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S226" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T226" s="3" t="s">
+        <v>1404</v>
+      </c>
+      <c r="U226" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="V226">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="227" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B227" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C227" t="s">
+        <v>1251</v>
+      </c>
+      <c r="D227" t="s">
+        <v>1252</v>
+      </c>
+      <c r="E227" t="s">
+        <v>1223</v>
+      </c>
+      <c r="F227" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I227">
+        <v>12</v>
+      </c>
+      <c r="L227">
+        <v>1410</v>
+      </c>
+      <c r="M227">
+        <v>275</v>
+      </c>
+      <c r="O227" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P227" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q227">
+        <v>2</v>
+      </c>
+      <c r="R227" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S227" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T227" s="3" t="s">
+        <v>1404</v>
+      </c>
+      <c r="U227" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="V227">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="228" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B228" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C228" t="s">
+        <v>1255</v>
+      </c>
+      <c r="D228" t="s">
+        <v>1256</v>
+      </c>
+      <c r="E228" t="s">
+        <v>1223</v>
+      </c>
+      <c r="F228" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I228">
+        <v>12</v>
+      </c>
+      <c r="L228">
+        <v>1510</v>
+      </c>
+      <c r="M228">
+        <v>275</v>
+      </c>
+      <c r="O228" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P228" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q228">
+        <v>2</v>
+      </c>
+      <c r="R228" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S228" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T228" s="3" t="s">
+        <v>1404</v>
+      </c>
+      <c r="U228" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="V228">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="229" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>1257</v>
+      </c>
+      <c r="B229" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C229" t="s">
+        <v>1259</v>
+      </c>
+      <c r="D229" t="s">
+        <v>1260</v>
+      </c>
+      <c r="E229" t="s">
+        <v>1223</v>
+      </c>
+      <c r="F229" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I229">
+        <v>12</v>
+      </c>
+      <c r="L229">
+        <v>1610</v>
+      </c>
+      <c r="M229">
+        <v>275</v>
+      </c>
+      <c r="O229" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P229" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q229">
+        <v>2</v>
+      </c>
+      <c r="R229" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S229" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T229" s="3" t="s">
+        <v>1404</v>
+      </c>
+      <c r="U229" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="V229">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="230" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B230" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C230" t="s">
+        <v>1263</v>
+      </c>
+      <c r="D230" t="s">
+        <v>1264</v>
+      </c>
+      <c r="E230" t="s">
+        <v>1223</v>
+      </c>
+      <c r="F230" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I230">
+        <v>12</v>
+      </c>
+      <c r="L230">
+        <v>1810</v>
+      </c>
+      <c r="M230">
+        <v>275</v>
+      </c>
+      <c r="O230" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P230" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q230">
+        <v>2</v>
+      </c>
+      <c r="R230" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S230" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T230" s="3" t="s">
+        <v>1404</v>
+      </c>
+      <c r="U230" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="V230">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="231" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B231" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C231" t="s">
+        <v>1267</v>
+      </c>
+      <c r="D231" t="s">
+        <v>1268</v>
+      </c>
+      <c r="E231" t="s">
+        <v>1223</v>
+      </c>
+      <c r="F231" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I231">
+        <v>12</v>
+      </c>
+      <c r="L231">
+        <v>2010</v>
+      </c>
+      <c r="M231">
+        <v>275</v>
+      </c>
+      <c r="O231" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P231" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q231">
+        <v>2</v>
+      </c>
+      <c r="R231" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S231" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T231" s="3" t="s">
+        <v>1404</v>
+      </c>
+      <c r="U231" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="V231">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="232" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B232" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C232" t="s">
+        <v>1271</v>
+      </c>
+      <c r="D232" t="s">
+        <v>1272</v>
+      </c>
+      <c r="E232" t="s">
+        <v>1223</v>
+      </c>
+      <c r="F232" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I232">
+        <v>12</v>
+      </c>
+      <c r="L232">
+        <v>2510</v>
+      </c>
+      <c r="M232">
+        <v>275</v>
+      </c>
+      <c r="O232" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P232" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q232">
+        <v>2</v>
+      </c>
+      <c r="R232" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S232" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T232" s="3" t="s">
+        <v>1404</v>
+      </c>
+      <c r="U232" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="V232">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="233" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B233" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C233" t="s">
+        <v>1275</v>
+      </c>
+      <c r="D233" t="s">
+        <v>1276</v>
+      </c>
+      <c r="E233" t="s">
+        <v>1223</v>
+      </c>
+      <c r="F233" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I233">
+        <v>12</v>
+      </c>
+      <c r="L233">
+        <v>3010</v>
+      </c>
+      <c r="M233">
+        <v>275</v>
+      </c>
+      <c r="O233" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P233" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q233">
+        <v>2</v>
+      </c>
+      <c r="R233" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S233" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T233" s="3" t="s">
+        <v>1404</v>
+      </c>
+      <c r="U233" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="V233">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="234" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B234" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C234" t="s">
+        <v>1227</v>
+      </c>
+      <c r="D234" t="s">
+        <v>1279</v>
+      </c>
+      <c r="E234" t="s">
+        <v>1280</v>
+      </c>
+      <c r="F234" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I234">
+        <v>12</v>
+      </c>
+      <c r="L234">
+        <v>410</v>
+      </c>
+      <c r="M234">
+        <v>275</v>
+      </c>
+      <c r="O234" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P234" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q234">
+        <v>2</v>
+      </c>
+      <c r="R234" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S234" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T234" s="3" t="s">
+        <v>1397</v>
+      </c>
+      <c r="U234" s="3" t="s">
+        <v>1406</v>
+      </c>
+      <c r="V234">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="235" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B235" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C235" t="s">
+        <v>1231</v>
+      </c>
+      <c r="D235" t="s">
+        <v>1283</v>
+      </c>
+      <c r="E235" t="s">
+        <v>1280</v>
+      </c>
+      <c r="F235" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I235">
+        <v>12</v>
+      </c>
+      <c r="L235">
+        <v>610</v>
+      </c>
+      <c r="M235">
+        <v>275</v>
+      </c>
+      <c r="O235" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P235" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q235">
+        <v>2</v>
+      </c>
+      <c r="R235" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S235" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T235" s="3" t="s">
+        <v>1397</v>
+      </c>
+      <c r="U235" s="3" t="s">
+        <v>1406</v>
+      </c>
+      <c r="V235">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="236" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B236" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C236" t="s">
+        <v>1235</v>
+      </c>
+      <c r="D236" t="s">
+        <v>1286</v>
+      </c>
+      <c r="E236" t="s">
+        <v>1280</v>
+      </c>
+      <c r="F236" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I236">
+        <v>12</v>
+      </c>
+      <c r="L236">
+        <v>810</v>
+      </c>
+      <c r="M236">
+        <v>275</v>
+      </c>
+      <c r="O236" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P236" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q236">
+        <v>2</v>
+      </c>
+      <c r="R236" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S236" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T236" s="3" t="s">
+        <v>1397</v>
+      </c>
+      <c r="U236" s="3" t="s">
+        <v>1406</v>
+      </c>
+      <c r="V236">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="237" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B237" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C237" t="s">
+        <v>1239</v>
+      </c>
+      <c r="D237" t="s">
+        <v>1289</v>
+      </c>
+      <c r="E237" t="s">
+        <v>1280</v>
+      </c>
+      <c r="F237" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I237">
+        <v>12</v>
+      </c>
+      <c r="L237">
+        <v>1010</v>
+      </c>
+      <c r="M237">
+        <v>275</v>
+      </c>
+      <c r="O237" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P237" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q237">
+        <v>2</v>
+      </c>
+      <c r="R237" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S237" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T237" s="3" t="s">
+        <v>1397</v>
+      </c>
+      <c r="U237" s="3" t="s">
+        <v>1406</v>
+      </c>
+      <c r="V237">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="238" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B238" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C238" t="s">
+        <v>1247</v>
+      </c>
+      <c r="D238" t="s">
+        <v>1292</v>
+      </c>
+      <c r="E238" t="s">
+        <v>1280</v>
+      </c>
+      <c r="F238" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I238">
+        <v>12</v>
+      </c>
+      <c r="L238">
+        <v>1210</v>
+      </c>
+      <c r="M238">
+        <v>275</v>
+      </c>
+      <c r="O238" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P238" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q238">
+        <v>2</v>
+      </c>
+      <c r="R238" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S238" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T238" s="3" t="s">
+        <v>1397</v>
+      </c>
+      <c r="U238" s="3" t="s">
+        <v>1406</v>
+      </c>
+      <c r="V238">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="239" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B239" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C239" t="s">
+        <v>1251</v>
+      </c>
+      <c r="D239" t="s">
+        <v>1295</v>
+      </c>
+      <c r="E239" t="s">
+        <v>1280</v>
+      </c>
+      <c r="F239" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I239">
+        <v>12</v>
+      </c>
+      <c r="L239">
+        <v>1410</v>
+      </c>
+      <c r="M239">
+        <v>275</v>
+      </c>
+      <c r="O239" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P239" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q239">
+        <v>2</v>
+      </c>
+      <c r="R239" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S239" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T239" s="3" t="s">
+        <v>1397</v>
+      </c>
+      <c r="U239" s="3" t="s">
+        <v>1406</v>
+      </c>
+      <c r="V239">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="240" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B240" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C240" t="s">
+        <v>1255</v>
+      </c>
+      <c r="D240" t="s">
+        <v>1298</v>
+      </c>
+      <c r="E240" t="s">
+        <v>1280</v>
+      </c>
+      <c r="F240" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I240">
+        <v>12</v>
+      </c>
+      <c r="L240">
+        <v>1510</v>
+      </c>
+      <c r="M240">
+        <v>275</v>
+      </c>
+      <c r="O240" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P240" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q240">
+        <v>2</v>
+      </c>
+      <c r="R240" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S240" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T240" s="3" t="s">
+        <v>1397</v>
+      </c>
+      <c r="U240" s="3" t="s">
+        <v>1406</v>
+      </c>
+      <c r="V240">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="241" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>1299</v>
+      </c>
+      <c r="B241" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C241" t="s">
+        <v>1259</v>
+      </c>
+      <c r="D241" t="s">
+        <v>1301</v>
+      </c>
+      <c r="E241" t="s">
+        <v>1280</v>
+      </c>
+      <c r="F241" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I241">
+        <v>12</v>
+      </c>
+      <c r="L241">
+        <v>1610</v>
+      </c>
+      <c r="M241">
+        <v>275</v>
+      </c>
+      <c r="O241" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P241" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q241">
+        <v>2</v>
+      </c>
+      <c r="R241" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S241" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T241" s="3" t="s">
+        <v>1397</v>
+      </c>
+      <c r="U241" s="3" t="s">
+        <v>1406</v>
+      </c>
+      <c r="V241">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="242" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B242" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C242" t="s">
+        <v>1267</v>
+      </c>
+      <c r="D242" t="s">
+        <v>1304</v>
+      </c>
+      <c r="E242" t="s">
+        <v>1280</v>
+      </c>
+      <c r="F242" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I242">
+        <v>12</v>
+      </c>
+      <c r="L242">
+        <v>2010</v>
+      </c>
+      <c r="M242">
+        <v>275</v>
+      </c>
+      <c r="O242" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P242" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q242">
+        <v>2</v>
+      </c>
+      <c r="R242" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S242" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T242" s="3" t="s">
+        <v>1397</v>
+      </c>
+      <c r="U242" s="3" t="s">
+        <v>1406</v>
+      </c>
+      <c r="V242">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="243" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>1305</v>
+      </c>
+      <c r="B243" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C243" t="s">
+        <v>1307</v>
+      </c>
+      <c r="D243" t="s">
+        <v>1308</v>
+      </c>
+      <c r="E243" t="s">
+        <v>1309</v>
+      </c>
+      <c r="F243" t="s">
+        <v>1310</v>
+      </c>
+      <c r="I243">
+        <v>16</v>
+      </c>
+      <c r="L243">
+        <v>210</v>
+      </c>
+      <c r="M243">
+        <v>250</v>
+      </c>
+      <c r="O243" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P243" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q243">
+        <v>2</v>
+      </c>
+      <c r="R243" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S243" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T243" s="3" t="s">
+        <v>1398</v>
+      </c>
+      <c r="U243" s="3" t="s">
+        <v>1407</v>
+      </c>
+      <c r="V243">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="244" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B244" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C244" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D244" t="s">
+        <v>1314</v>
+      </c>
+      <c r="E244" t="s">
+        <v>1309</v>
+      </c>
+      <c r="F244" t="s">
+        <v>1310</v>
+      </c>
+      <c r="I244">
+        <v>16</v>
+      </c>
+      <c r="L244">
+        <v>610</v>
+      </c>
+      <c r="M244">
+        <v>250</v>
+      </c>
+      <c r="O244" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P244" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q244">
+        <v>2</v>
+      </c>
+      <c r="R244" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S244" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T244" s="3" t="s">
+        <v>1398</v>
+      </c>
+      <c r="U244" s="3" t="s">
+        <v>1407</v>
+      </c>
+      <c r="V244">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="245" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B245" t="s">
+        <v>1316</v>
+      </c>
+      <c r="C245" t="s">
+        <v>1317</v>
+      </c>
+      <c r="D245" t="s">
+        <v>1318</v>
+      </c>
+      <c r="E245" t="s">
+        <v>1309</v>
+      </c>
+      <c r="F245" t="s">
+        <v>1310</v>
+      </c>
+      <c r="I245">
+        <v>16</v>
+      </c>
+      <c r="L245">
+        <v>810</v>
+      </c>
+      <c r="M245">
+        <v>250</v>
+      </c>
+      <c r="O245" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P245" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q245">
+        <v>2</v>
+      </c>
+      <c r="R245" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S245" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T245" s="3" t="s">
+        <v>1398</v>
+      </c>
+      <c r="U245" s="3" t="s">
+        <v>1407</v>
+      </c>
+      <c r="V245">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="246" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B246" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C246" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D246" t="s">
+        <v>1322</v>
+      </c>
+      <c r="E246" t="s">
+        <v>1309</v>
+      </c>
+      <c r="F246" t="s">
+        <v>1310</v>
+      </c>
+      <c r="I246">
+        <v>16</v>
+      </c>
+      <c r="L246">
+        <v>1010</v>
+      </c>
+      <c r="M246">
+        <v>250</v>
+      </c>
+      <c r="O246" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P246" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q246">
+        <v>2</v>
+      </c>
+      <c r="R246" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S246" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T246" s="3" t="s">
+        <v>1398</v>
+      </c>
+      <c r="U246" s="3" t="s">
+        <v>1407</v>
+      </c>
+      <c r="V246">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="247" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B247" t="s">
+        <v>1324</v>
+      </c>
+      <c r="C247" t="s">
+        <v>1325</v>
+      </c>
+      <c r="D247" t="s">
+        <v>1326</v>
+      </c>
+      <c r="E247" t="s">
+        <v>1309</v>
+      </c>
+      <c r="F247" t="s">
+        <v>1310</v>
+      </c>
+      <c r="I247">
+        <v>16</v>
+      </c>
+      <c r="L247">
+        <v>1210</v>
+      </c>
+      <c r="M247">
+        <v>250</v>
+      </c>
+      <c r="O247" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P247" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q247">
+        <v>2</v>
+      </c>
+      <c r="R247" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S247" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T247" s="3" t="s">
+        <v>1398</v>
+      </c>
+      <c r="U247" s="3" t="s">
+        <v>1407</v>
+      </c>
+      <c r="V247">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="248" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B248" t="s">
+        <v>1328</v>
+      </c>
+      <c r="C248" t="s">
+        <v>1329</v>
+      </c>
+      <c r="D248" t="s">
+        <v>1330</v>
+      </c>
+      <c r="E248" t="s">
+        <v>1309</v>
+      </c>
+      <c r="F248" t="s">
+        <v>1310</v>
+      </c>
+      <c r="I248">
+        <v>16</v>
+      </c>
+      <c r="L248">
+        <v>1410</v>
+      </c>
+      <c r="M248">
+        <v>250</v>
+      </c>
+      <c r="O248" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P248" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q248">
+        <v>2</v>
+      </c>
+      <c r="R248" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S248" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T248" s="3" t="s">
+        <v>1398</v>
+      </c>
+      <c r="U248" s="3" t="s">
+        <v>1407</v>
+      </c>
+      <c r="V248">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="249" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B249" t="s">
+        <v>1332</v>
+      </c>
+      <c r="C249" t="s">
+        <v>1333</v>
+      </c>
+      <c r="D249" t="s">
+        <v>1334</v>
+      </c>
+      <c r="E249" t="s">
+        <v>1309</v>
+      </c>
+      <c r="F249" t="s">
+        <v>1310</v>
+      </c>
+      <c r="I249">
+        <v>16</v>
+      </c>
+      <c r="L249">
+        <v>1510</v>
+      </c>
+      <c r="M249">
+        <v>250</v>
+      </c>
+      <c r="O249" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P249" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q249">
+        <v>2</v>
+      </c>
+      <c r="R249" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S249" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T249" s="3" t="s">
+        <v>1398</v>
+      </c>
+      <c r="U249" s="3" t="s">
+        <v>1407</v>
+      </c>
+      <c r="V249">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="250" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B250" t="s">
+        <v>1336</v>
+      </c>
+      <c r="C250" t="s">
+        <v>1337</v>
+      </c>
+      <c r="D250" t="s">
+        <v>1338</v>
+      </c>
+      <c r="E250" t="s">
+        <v>1309</v>
+      </c>
+      <c r="F250" t="s">
+        <v>1310</v>
+      </c>
+      <c r="I250">
+        <v>16</v>
+      </c>
+      <c r="L250">
+        <v>1610</v>
+      </c>
+      <c r="M250">
+        <v>250</v>
+      </c>
+      <c r="O250" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P250" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q250">
+        <v>2</v>
+      </c>
+      <c r="R250" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S250" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T250" s="3" t="s">
+        <v>1398</v>
+      </c>
+      <c r="U250" s="3" t="s">
+        <v>1407</v>
+      </c>
+      <c r="V250">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="251" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B251" t="s">
+        <v>1340</v>
+      </c>
+      <c r="C251" t="s">
+        <v>1341</v>
+      </c>
+      <c r="D251" t="s">
+        <v>1342</v>
+      </c>
+      <c r="E251" t="s">
+        <v>1309</v>
+      </c>
+      <c r="F251" t="s">
+        <v>1310</v>
+      </c>
+      <c r="I251">
+        <v>16</v>
+      </c>
+      <c r="L251">
+        <v>1810</v>
+      </c>
+      <c r="M251">
+        <v>250</v>
+      </c>
+      <c r="O251" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P251" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q251">
+        <v>2</v>
+      </c>
+      <c r="R251" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S251" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T251" s="3" t="s">
+        <v>1398</v>
+      </c>
+      <c r="U251" s="3" t="s">
+        <v>1407</v>
+      </c>
+      <c r="V251">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="252" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B252" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C252" t="s">
+        <v>1345</v>
+      </c>
+      <c r="D252" t="s">
+        <v>1346</v>
+      </c>
+      <c r="E252" t="s">
+        <v>1309</v>
+      </c>
+      <c r="F252" t="s">
+        <v>1310</v>
+      </c>
+      <c r="I252">
+        <v>16</v>
+      </c>
+      <c r="L252">
+        <v>2010</v>
+      </c>
+      <c r="M252">
+        <v>250</v>
+      </c>
+      <c r="O252" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P252" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q252">
+        <v>2</v>
+      </c>
+      <c r="R252" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S252" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T252" s="3" t="s">
+        <v>1398</v>
+      </c>
+      <c r="U252" s="3" t="s">
+        <v>1407</v>
+      </c>
+      <c r="V252">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="253" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>1347</v>
+      </c>
+      <c r="B253" t="s">
+        <v>1348</v>
+      </c>
+      <c r="C253" t="s">
+        <v>1349</v>
+      </c>
+      <c r="D253" t="s">
+        <v>1350</v>
+      </c>
+      <c r="E253" t="s">
+        <v>1351</v>
+      </c>
+      <c r="F253" t="s">
+        <v>1352</v>
+      </c>
+      <c r="I253">
+        <v>19</v>
+      </c>
+      <c r="L253">
+        <v>1010</v>
+      </c>
+      <c r="M253">
+        <v>215</v>
+      </c>
+      <c r="O253" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P253" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q253">
+        <v>2</v>
+      </c>
+      <c r="R253" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S253" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T253" s="3" t="s">
+        <v>1399</v>
+      </c>
+      <c r="U253" s="3" t="s">
+        <v>1408</v>
+      </c>
+      <c r="V253">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="254" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>1353</v>
+      </c>
+      <c r="B254" t="s">
+        <v>1354</v>
+      </c>
+      <c r="C254" t="s">
+        <v>1355</v>
+      </c>
+      <c r="D254" t="s">
+        <v>1356</v>
+      </c>
+      <c r="E254" t="s">
+        <v>1357</v>
+      </c>
+      <c r="F254" t="s">
+        <v>1358</v>
+      </c>
+      <c r="I254">
+        <v>20</v>
+      </c>
+      <c r="L254">
+        <v>1210</v>
+      </c>
+      <c r="M254">
+        <v>215</v>
+      </c>
+      <c r="O254" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P254" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q254">
+        <v>2</v>
+      </c>
+      <c r="R254" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S254" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T254" s="3" t="s">
+        <v>1399</v>
+      </c>
+      <c r="U254" s="3" t="s">
+        <v>1408</v>
+      </c>
+      <c r="V254">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="255" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>1359</v>
+      </c>
+      <c r="B255" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C255" t="s">
+        <v>1361</v>
+      </c>
+      <c r="D255" t="s">
+        <v>1362</v>
+      </c>
+      <c r="E255" t="s">
+        <v>1357</v>
+      </c>
+      <c r="F255" t="s">
+        <v>1358</v>
+      </c>
+      <c r="I255">
+        <v>20</v>
+      </c>
+      <c r="L255">
+        <v>1510</v>
+      </c>
+      <c r="M255">
+        <v>215</v>
+      </c>
+      <c r="O255" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P255" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q255">
+        <v>2</v>
+      </c>
+      <c r="R255" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S255" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T255" s="3" t="s">
+        <v>1399</v>
+      </c>
+      <c r="U255" s="3" t="s">
+        <v>1408</v>
+      </c>
+      <c r="V255">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="256" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>1363</v>
+      </c>
+      <c r="B256" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C256" t="s">
+        <v>1365</v>
+      </c>
+      <c r="D256" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E256" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F256" t="s">
+        <v>1182</v>
+      </c>
+      <c r="I256">
+        <v>10</v>
+      </c>
+      <c r="L256">
+        <v>1000</v>
+      </c>
+      <c r="O256" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P256" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q256">
+        <v>2</v>
+      </c>
+      <c r="R256" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S256" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T256" s="3" t="s">
+        <v>1404</v>
+      </c>
+      <c r="U256" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="V256">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="257" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>1368</v>
+      </c>
+      <c r="B257" t="s">
+        <v>1369</v>
+      </c>
+      <c r="C257" t="s">
+        <v>1370</v>
+      </c>
+      <c r="D257" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E257" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F257" t="s">
+        <v>1182</v>
+      </c>
+      <c r="I257">
+        <v>10</v>
+      </c>
+      <c r="L257">
+        <v>1200</v>
+      </c>
+      <c r="O257" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P257" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q257">
+        <v>2</v>
+      </c>
+      <c r="R257" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S257" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T257" s="3" t="s">
+        <v>1404</v>
+      </c>
+      <c r="U257" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="V257">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="258" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B258" t="s">
+        <v>1373</v>
+      </c>
+      <c r="C258" t="s">
+        <v>1374</v>
+      </c>
+      <c r="D258" t="s">
+        <v>1375</v>
+      </c>
+      <c r="E258" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F258" t="s">
+        <v>1182</v>
+      </c>
+      <c r="I258">
+        <v>10</v>
+      </c>
+      <c r="L258">
+        <v>1500</v>
+      </c>
+      <c r="O258" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P258" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q258">
+        <v>2</v>
+      </c>
+      <c r="R258" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S258" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T258" s="3" t="s">
+        <v>1404</v>
+      </c>
+      <c r="U258" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="V258">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="259" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B259" t="s">
+        <v>1377</v>
+      </c>
+      <c r="C259" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D259" t="s">
+        <v>1379</v>
+      </c>
+      <c r="E259" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F259" t="s">
+        <v>1182</v>
+      </c>
+      <c r="I259">
+        <v>10</v>
+      </c>
+      <c r="L259">
+        <v>1800</v>
+      </c>
+      <c r="O259" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P259" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q259">
+        <v>2</v>
+      </c>
+      <c r="R259" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S259" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T259" s="3" t="s">
+        <v>1404</v>
+      </c>
+      <c r="U259" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="V259">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="260" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B260" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C260" t="s">
+        <v>1382</v>
+      </c>
+      <c r="D260" t="s">
+        <v>1383</v>
+      </c>
+      <c r="E260" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F260" t="s">
+        <v>1182</v>
+      </c>
+      <c r="I260">
+        <v>10</v>
+      </c>
+      <c r="L260">
+        <v>420</v>
+      </c>
+      <c r="O260" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P260" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q260">
+        <v>2</v>
+      </c>
+      <c r="R260" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S260" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T260" s="3" t="s">
+        <v>1404</v>
+      </c>
+      <c r="U260" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="V260">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="261" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>1384</v>
+      </c>
+      <c r="B261" t="s">
+        <v>1385</v>
+      </c>
+      <c r="C261" t="s">
+        <v>1386</v>
+      </c>
+      <c r="D261" t="s">
+        <v>1387</v>
+      </c>
+      <c r="E261" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F261" t="s">
+        <v>1182</v>
+      </c>
+      <c r="I261">
+        <v>10</v>
+      </c>
+      <c r="L261">
+        <v>600</v>
+      </c>
+      <c r="O261" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P261" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q261">
+        <v>2</v>
+      </c>
+      <c r="R261" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S261" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T261" s="3" t="s">
+        <v>1404</v>
+      </c>
+      <c r="U261" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="V261">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="262" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B262" t="s">
+        <v>1389</v>
+      </c>
+      <c r="C262" t="s">
+        <v>1390</v>
+      </c>
+      <c r="D262" t="s">
+        <v>1391</v>
+      </c>
+      <c r="E262" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F262" t="s">
+        <v>1182</v>
+      </c>
+      <c r="I262">
+        <v>10</v>
+      </c>
+      <c r="L262">
+        <v>800</v>
+      </c>
+      <c r="O262" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="P262" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Q262">
+        <v>2</v>
+      </c>
+      <c r="R262" t="s">
+        <v>1394</v>
+      </c>
+      <c r="S262" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="T262" s="3" t="s">
+        <v>1404</v>
+      </c>
+      <c r="U262" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="V262">
+        <v>189</v>
       </c>
     </row>
   </sheetData>
